--- a/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I732"/>
+  <dimension ref="A1:J732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>Pair</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tissue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,6 +519,7 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +560,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -594,6 +601,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -634,6 +642,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -674,6 +683,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -714,6 +724,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -754,6 +765,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -794,6 +806,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -834,6 +847,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -874,6 +888,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -914,6 +929,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -954,6 +970,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -994,6 +1011,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1034,6 +1052,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1074,6 +1093,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1114,6 +1134,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1154,6 +1175,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1194,6 +1216,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1234,6 +1257,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1274,6 +1298,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1314,6 +1339,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1354,6 +1380,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1394,6 +1421,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1434,6 +1462,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1474,6 +1503,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1514,6 +1544,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1554,6 +1585,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1592,6 +1624,11 @@
           <t>(1,2)</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1630,6 +1667,11 @@
           <t>(1,3)</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1668,6 +1710,11 @@
           <t>(1,4)</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1706,6 +1753,11 @@
           <t>(1,5)</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1744,6 +1796,11 @@
           <t>(1,6)</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1782,6 +1839,11 @@
           <t>(2,3)</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1820,6 +1882,11 @@
           <t>(2,4)</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1858,6 +1925,11 @@
           <t>(2,5)</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1896,6 +1968,11 @@
           <t>(2,6)</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1934,6 +2011,11 @@
           <t>(3,4)</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1972,6 +2054,11 @@
           <t>(3,5)</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2010,6 +2097,11 @@
           <t>(3,6)</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2048,6 +2140,11 @@
           <t>(4,5)</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2086,6 +2183,11 @@
           <t>(4,6)</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2124,6 +2226,11 @@
           <t>(5,6)</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2162,6 +2269,11 @@
           <t>(7,8)</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2200,6 +2312,11 @@
           <t>(7,9)</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2238,6 +2355,11 @@
           <t>(8,9)</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2276,6 +2398,11 @@
           <t>(10,11)</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2314,6 +2441,11 @@
           <t>(10,12)</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2352,6 +2484,11 @@
           <t>(10,13)</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2390,6 +2527,11 @@
           <t>(10,14)</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2428,6 +2570,11 @@
           <t>(10,15)</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2466,6 +2613,11 @@
           <t>(11,12)</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2504,6 +2656,11 @@
           <t>(11,13)</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2542,6 +2699,11 @@
           <t>(11,14)</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2580,6 +2742,11 @@
           <t>(11,15)</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2618,6 +2785,11 @@
           <t>(12,13)</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2656,6 +2828,11 @@
           <t>(12,14)</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2694,6 +2871,11 @@
           <t>(12,15)</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2732,6 +2914,11 @@
           <t>(13,14)</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2770,6 +2957,11 @@
           <t>(13,15)</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2808,6 +3000,11 @@
           <t>(14,15)</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2846,6 +3043,11 @@
           <t>(16,17)</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2884,6 +3086,11 @@
           <t>(16,18)</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2922,6 +3129,11 @@
           <t>(17,18)</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2960,6 +3172,11 @@
           <t>(19,20)</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2998,6 +3215,11 @@
           <t>(19,21)</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3036,6 +3258,11 @@
           <t>(19,22)</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3074,6 +3301,11 @@
           <t>(19,23)</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3112,6 +3344,11 @@
           <t>(19,24)</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3150,6 +3387,11 @@
           <t>(20,21)</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3188,6 +3430,11 @@
           <t>(20,22)</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3226,6 +3473,11 @@
           <t>(20,23)</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3264,6 +3516,11 @@
           <t>(20,24)</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3302,6 +3559,11 @@
           <t>(21,22)</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3340,6 +3602,11 @@
           <t>(21,23)</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3378,6 +3645,11 @@
           <t>(21,24)</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3416,6 +3688,11 @@
           <t>(22,23)</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3454,6 +3731,11 @@
           <t>(22,24)</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3492,6 +3774,11 @@
           <t>(23,24)</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3530,6 +3817,11 @@
           <t>(25,26)</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3568,6 +3860,11 @@
           <t>(25,27)</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3604,6 +3901,11 @@
       <c r="I82" t="inlineStr">
         <is>
           <t>(26,27)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3640,6 +3942,7 @@
           <t>(1,2)</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3674,6 +3977,7 @@
           <t>(1,3)</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3708,6 +4012,7 @@
           <t>(1,4)</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3742,6 +4047,7 @@
           <t>(1,5)</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3776,6 +4082,7 @@
           <t>(1,6)</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3810,6 +4117,7 @@
           <t>(1,7)</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3844,6 +4152,7 @@
           <t>(1,8)</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3878,6 +4187,7 @@
           <t>(1,9)</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3912,6 +4222,7 @@
           <t>(2,3)</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3946,6 +4257,7 @@
           <t>(2,4)</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3980,6 +4292,7 @@
           <t>(2,5)</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4014,6 +4327,7 @@
           <t>(2,6)</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4048,6 +4362,7 @@
           <t>(2,7)</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4082,6 +4397,7 @@
           <t>(2,8)</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4116,6 +4432,7 @@
           <t>(2,9)</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4150,6 +4467,7 @@
           <t>(3,4)</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4184,6 +4502,7 @@
           <t>(3,5)</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4218,6 +4537,7 @@
           <t>(3,6)</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4252,6 +4572,7 @@
           <t>(3,7)</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4286,6 +4607,7 @@
           <t>(3,8)</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4320,6 +4642,7 @@
           <t>(3,9)</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4354,6 +4677,7 @@
           <t>(4,5)</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4388,6 +4712,7 @@
           <t>(4,6)</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4422,6 +4747,7 @@
           <t>(4,7)</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4456,6 +4782,7 @@
           <t>(4,8)</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4490,6 +4817,7 @@
           <t>(4,9)</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4524,6 +4852,7 @@
           <t>(5,6)</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4558,6 +4887,7 @@
           <t>(5,7)</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4592,6 +4922,7 @@
           <t>(5,8)</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4626,6 +4957,7 @@
           <t>(5,9)</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4660,6 +4992,7 @@
           <t>(6,7)</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4694,6 +5027,7 @@
           <t>(6,8)</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4728,6 +5062,7 @@
           <t>(6,9)</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4762,6 +5097,7 @@
           <t>(7,8)</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4796,6 +5132,7 @@
           <t>(7,9)</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4830,6 +5167,7 @@
           <t>(8,9)</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4864,6 +5202,7 @@
           <t>(10,11)</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4898,6 +5237,7 @@
           <t>(10,12)</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4932,6 +5272,7 @@
           <t>(10,13)</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4966,6 +5307,7 @@
           <t>(10,14)</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5000,6 +5342,7 @@
           <t>(10,15)</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5034,6 +5377,7 @@
           <t>(10,16)</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5068,6 +5412,7 @@
           <t>(10,17)</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5102,6 +5447,7 @@
           <t>(10,18)</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5136,6 +5482,7 @@
           <t>(11,12)</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5170,6 +5517,7 @@
           <t>(11,13)</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5204,6 +5552,7 @@
           <t>(11,14)</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5238,6 +5587,7 @@
           <t>(11,15)</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5272,6 +5622,7 @@
           <t>(11,16)</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5306,6 +5657,7 @@
           <t>(11,17)</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5340,6 +5692,7 @@
           <t>(11,18)</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5374,6 +5727,7 @@
           <t>(12,13)</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5408,6 +5762,7 @@
           <t>(12,14)</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5442,6 +5797,7 @@
           <t>(12,15)</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5476,6 +5832,7 @@
           <t>(12,16)</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5510,6 +5867,7 @@
           <t>(12,17)</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5544,6 +5902,7 @@
           <t>(12,18)</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5578,6 +5937,7 @@
           <t>(13,14)</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5612,6 +5972,7 @@
           <t>(13,15)</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5646,6 +6007,7 @@
           <t>(13,16)</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5680,6 +6042,7 @@
           <t>(13,17)</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5714,6 +6077,7 @@
           <t>(13,18)</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5748,6 +6112,7 @@
           <t>(14,15)</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5782,6 +6147,7 @@
           <t>(14,16)</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5816,6 +6182,7 @@
           <t>(14,17)</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5850,6 +6217,7 @@
           <t>(14,18)</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5884,6 +6252,7 @@
           <t>(15,16)</t>
         </is>
       </c>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5918,6 +6287,7 @@
           <t>(15,17)</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5952,6 +6322,7 @@
           <t>(15,18)</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5986,6 +6357,7 @@
           <t>(16,17)</t>
         </is>
       </c>
+      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6020,6 +6392,7 @@
           <t>(16,18)</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6054,6 +6427,7 @@
           <t>(17,18)</t>
         </is>
       </c>
+      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6088,6 +6462,7 @@
           <t>(19,20)</t>
         </is>
       </c>
+      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6122,6 +6497,7 @@
           <t>(19,21)</t>
         </is>
       </c>
+      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6156,6 +6532,7 @@
           <t>(19,22)</t>
         </is>
       </c>
+      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6190,6 +6567,7 @@
           <t>(19,23)</t>
         </is>
       </c>
+      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6224,6 +6602,7 @@
           <t>(19,24)</t>
         </is>
       </c>
+      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6258,6 +6637,7 @@
           <t>(19,25)</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6292,6 +6672,7 @@
           <t>(19,26)</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6326,6 +6707,7 @@
           <t>(19,27)</t>
         </is>
       </c>
+      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6360,6 +6742,7 @@
           <t>(20,21)</t>
         </is>
       </c>
+      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6394,6 +6777,7 @@
           <t>(20,22)</t>
         </is>
       </c>
+      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6428,6 +6812,7 @@
           <t>(20,23)</t>
         </is>
       </c>
+      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6462,6 +6847,7 @@
           <t>(20,24)</t>
         </is>
       </c>
+      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6496,6 +6882,7 @@
           <t>(20,25)</t>
         </is>
       </c>
+      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6530,6 +6917,7 @@
           <t>(20,26)</t>
         </is>
       </c>
+      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6564,6 +6952,7 @@
           <t>(20,27)</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6598,6 +6987,7 @@
           <t>(21,22)</t>
         </is>
       </c>
+      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6632,6 +7022,7 @@
           <t>(21,23)</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6666,6 +7057,7 @@
           <t>(21,24)</t>
         </is>
       </c>
+      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6700,6 +7092,7 @@
           <t>(21,25)</t>
         </is>
       </c>
+      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6734,6 +7127,7 @@
           <t>(21,26)</t>
         </is>
       </c>
+      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6768,6 +7162,7 @@
           <t>(21,27)</t>
         </is>
       </c>
+      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6802,6 +7197,7 @@
           <t>(22,23)</t>
         </is>
       </c>
+      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6836,6 +7232,7 @@
           <t>(22,24)</t>
         </is>
       </c>
+      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6870,6 +7267,7 @@
           <t>(22,25)</t>
         </is>
       </c>
+      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6904,6 +7302,7 @@
           <t>(22,26)</t>
         </is>
       </c>
+      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6938,6 +7337,7 @@
           <t>(22,27)</t>
         </is>
       </c>
+      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6972,6 +7372,7 @@
           <t>(23,24)</t>
         </is>
       </c>
+      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7006,6 +7407,7 @@
           <t>(23,25)</t>
         </is>
       </c>
+      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7040,6 +7442,7 @@
           <t>(23,26)</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7074,6 +7477,7 @@
           <t>(23,27)</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7108,6 +7512,7 @@
           <t>(24,25)</t>
         </is>
       </c>
+      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7142,6 +7547,7 @@
           <t>(24,26)</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7176,6 +7582,7 @@
           <t>(24,27)</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7210,6 +7617,7 @@
           <t>(25,26)</t>
         </is>
       </c>
+      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7244,6 +7652,7 @@
           <t>(25,27)</t>
         </is>
       </c>
+      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7278,6 +7687,7 @@
           <t>(26,27)</t>
         </is>
       </c>
+      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7312,6 +7722,7 @@
           <t>(1,2)</t>
         </is>
       </c>
+      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7346,6 +7757,7 @@
           <t>(1,3)</t>
         </is>
       </c>
+      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7380,6 +7792,7 @@
           <t>(1,4)</t>
         </is>
       </c>
+      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7414,6 +7827,7 @@
           <t>(1,5)</t>
         </is>
       </c>
+      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7448,6 +7862,7 @@
           <t>(1,6)</t>
         </is>
       </c>
+      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7482,6 +7897,7 @@
           <t>(1,10)</t>
         </is>
       </c>
+      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7516,6 +7932,7 @@
           <t>(1,11)</t>
         </is>
       </c>
+      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7550,6 +7967,7 @@
           <t>(1,12)</t>
         </is>
       </c>
+      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7584,6 +8002,7 @@
           <t>(1,13)</t>
         </is>
       </c>
+      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7618,6 +8037,7 @@
           <t>(1,14)</t>
         </is>
       </c>
+      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7652,6 +8072,7 @@
           <t>(1,15)</t>
         </is>
       </c>
+      <c r="J201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7686,6 +8107,7 @@
           <t>(1,19)</t>
         </is>
       </c>
+      <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7720,6 +8142,7 @@
           <t>(1,20)</t>
         </is>
       </c>
+      <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7754,6 +8177,7 @@
           <t>(1,21)</t>
         </is>
       </c>
+      <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7788,6 +8212,7 @@
           <t>(1,22)</t>
         </is>
       </c>
+      <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7822,6 +8247,7 @@
           <t>(1,23)</t>
         </is>
       </c>
+      <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7856,6 +8282,7 @@
           <t>(1,24)</t>
         </is>
       </c>
+      <c r="J207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7890,6 +8317,7 @@
           <t>(2,3)</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7924,6 +8352,7 @@
           <t>(2,4)</t>
         </is>
       </c>
+      <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7958,6 +8387,7 @@
           <t>(2,5)</t>
         </is>
       </c>
+      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7992,6 +8422,7 @@
           <t>(2,6)</t>
         </is>
       </c>
+      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8026,6 +8457,7 @@
           <t>(2,10)</t>
         </is>
       </c>
+      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8060,6 +8492,7 @@
           <t>(2,11)</t>
         </is>
       </c>
+      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8094,6 +8527,7 @@
           <t>(2,12)</t>
         </is>
       </c>
+      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8128,6 +8562,7 @@
           <t>(2,13)</t>
         </is>
       </c>
+      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8162,6 +8597,7 @@
           <t>(2,14)</t>
         </is>
       </c>
+      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8196,6 +8632,7 @@
           <t>(2,15)</t>
         </is>
       </c>
+      <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8230,6 +8667,7 @@
           <t>(2,19)</t>
         </is>
       </c>
+      <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8264,6 +8702,7 @@
           <t>(2,20)</t>
         </is>
       </c>
+      <c r="J219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8298,6 +8737,7 @@
           <t>(2,21)</t>
         </is>
       </c>
+      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8332,6 +8772,7 @@
           <t>(2,22)</t>
         </is>
       </c>
+      <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8366,6 +8807,7 @@
           <t>(2,23)</t>
         </is>
       </c>
+      <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8400,6 +8842,7 @@
           <t>(2,24)</t>
         </is>
       </c>
+      <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8434,6 +8877,7 @@
           <t>(3,4)</t>
         </is>
       </c>
+      <c r="J224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8468,6 +8912,7 @@
           <t>(3,5)</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8502,6 +8947,7 @@
           <t>(3,6)</t>
         </is>
       </c>
+      <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8536,6 +8982,7 @@
           <t>(3,10)</t>
         </is>
       </c>
+      <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8570,6 +9017,7 @@
           <t>(3,11)</t>
         </is>
       </c>
+      <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8604,6 +9052,7 @@
           <t>(3,12)</t>
         </is>
       </c>
+      <c r="J229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8638,6 +9087,7 @@
           <t>(3,13)</t>
         </is>
       </c>
+      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8672,6 +9122,7 @@
           <t>(3,14)</t>
         </is>
       </c>
+      <c r="J231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8706,6 +9157,7 @@
           <t>(3,15)</t>
         </is>
       </c>
+      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8740,6 +9192,7 @@
           <t>(3,19)</t>
         </is>
       </c>
+      <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8774,6 +9227,7 @@
           <t>(3,20)</t>
         </is>
       </c>
+      <c r="J234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8808,6 +9262,7 @@
           <t>(3,21)</t>
         </is>
       </c>
+      <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8842,6 +9297,7 @@
           <t>(3,22)</t>
         </is>
       </c>
+      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8876,6 +9332,7 @@
           <t>(3,23)</t>
         </is>
       </c>
+      <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8910,6 +9367,7 @@
           <t>(3,24)</t>
         </is>
       </c>
+      <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8944,6 +9402,7 @@
           <t>(4,5)</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8978,6 +9437,7 @@
           <t>(4,6)</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9012,6 +9472,7 @@
           <t>(4,10)</t>
         </is>
       </c>
+      <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9046,6 +9507,7 @@
           <t>(4,11)</t>
         </is>
       </c>
+      <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9080,6 +9542,7 @@
           <t>(4,12)</t>
         </is>
       </c>
+      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9114,6 +9577,7 @@
           <t>(4,13)</t>
         </is>
       </c>
+      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9148,6 +9612,7 @@
           <t>(4,14)</t>
         </is>
       </c>
+      <c r="J245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9182,6 +9647,7 @@
           <t>(4,15)</t>
         </is>
       </c>
+      <c r="J246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9216,6 +9682,7 @@
           <t>(4,19)</t>
         </is>
       </c>
+      <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9250,6 +9717,7 @@
           <t>(4,20)</t>
         </is>
       </c>
+      <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9284,6 +9752,7 @@
           <t>(4,21)</t>
         </is>
       </c>
+      <c r="J249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9318,6 +9787,7 @@
           <t>(4,22)</t>
         </is>
       </c>
+      <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9352,6 +9822,7 @@
           <t>(4,23)</t>
         </is>
       </c>
+      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9386,6 +9857,7 @@
           <t>(4,24)</t>
         </is>
       </c>
+      <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9420,6 +9892,7 @@
           <t>(5,6)</t>
         </is>
       </c>
+      <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9454,6 +9927,7 @@
           <t>(5,10)</t>
         </is>
       </c>
+      <c r="J254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9488,6 +9962,7 @@
           <t>(5,11)</t>
         </is>
       </c>
+      <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9522,6 +9997,7 @@
           <t>(5,12)</t>
         </is>
       </c>
+      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9556,6 +10032,7 @@
           <t>(5,13)</t>
         </is>
       </c>
+      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9590,6 +10067,7 @@
           <t>(5,14)</t>
         </is>
       </c>
+      <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9624,6 +10102,7 @@
           <t>(5,15)</t>
         </is>
       </c>
+      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9658,6 +10137,7 @@
           <t>(5,19)</t>
         </is>
       </c>
+      <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9692,6 +10172,7 @@
           <t>(5,20)</t>
         </is>
       </c>
+      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9726,6 +10207,7 @@
           <t>(5,21)</t>
         </is>
       </c>
+      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9760,6 +10242,7 @@
           <t>(5,22)</t>
         </is>
       </c>
+      <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9794,6 +10277,7 @@
           <t>(5,23)</t>
         </is>
       </c>
+      <c r="J264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9828,6 +10312,7 @@
           <t>(5,24)</t>
         </is>
       </c>
+      <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9862,6 +10347,7 @@
           <t>(6,10)</t>
         </is>
       </c>
+      <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9896,6 +10382,7 @@
           <t>(6,11)</t>
         </is>
       </c>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9930,6 +10417,7 @@
           <t>(6,12)</t>
         </is>
       </c>
+      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9964,6 +10452,7 @@
           <t>(6,13)</t>
         </is>
       </c>
+      <c r="J269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9998,6 +10487,7 @@
           <t>(6,14)</t>
         </is>
       </c>
+      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10032,6 +10522,7 @@
           <t>(6,15)</t>
         </is>
       </c>
+      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10066,6 +10557,7 @@
           <t>(6,19)</t>
         </is>
       </c>
+      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10100,6 +10592,7 @@
           <t>(6,20)</t>
         </is>
       </c>
+      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10134,6 +10627,7 @@
           <t>(6,21)</t>
         </is>
       </c>
+      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10168,6 +10662,7 @@
           <t>(6,22)</t>
         </is>
       </c>
+      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10202,6 +10697,7 @@
           <t>(6,23)</t>
         </is>
       </c>
+      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10236,6 +10732,7 @@
           <t>(6,24)</t>
         </is>
       </c>
+      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10270,6 +10767,7 @@
           <t>(10,11)</t>
         </is>
       </c>
+      <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10304,6 +10802,7 @@
           <t>(10,12)</t>
         </is>
       </c>
+      <c r="J279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10338,6 +10837,7 @@
           <t>(10,13)</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10372,6 +10872,7 @@
           <t>(10,14)</t>
         </is>
       </c>
+      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10406,6 +10907,7 @@
           <t>(10,15)</t>
         </is>
       </c>
+      <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10440,6 +10942,7 @@
           <t>(10,19)</t>
         </is>
       </c>
+      <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10474,6 +10977,7 @@
           <t>(10,20)</t>
         </is>
       </c>
+      <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10508,6 +11012,7 @@
           <t>(10,21)</t>
         </is>
       </c>
+      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10542,6 +11047,7 @@
           <t>(10,22)</t>
         </is>
       </c>
+      <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10576,6 +11082,7 @@
           <t>(10,23)</t>
         </is>
       </c>
+      <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10610,6 +11117,7 @@
           <t>(10,24)</t>
         </is>
       </c>
+      <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10644,6 +11152,7 @@
           <t>(11,12)</t>
         </is>
       </c>
+      <c r="J289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10678,6 +11187,7 @@
           <t>(11,13)</t>
         </is>
       </c>
+      <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10712,6 +11222,7 @@
           <t>(11,14)</t>
         </is>
       </c>
+      <c r="J291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10746,6 +11257,7 @@
           <t>(11,15)</t>
         </is>
       </c>
+      <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10780,6 +11292,7 @@
           <t>(11,19)</t>
         </is>
       </c>
+      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10814,6 +11327,7 @@
           <t>(11,20)</t>
         </is>
       </c>
+      <c r="J294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10848,6 +11362,7 @@
           <t>(11,21)</t>
         </is>
       </c>
+      <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10882,6 +11397,7 @@
           <t>(11,22)</t>
         </is>
       </c>
+      <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10916,6 +11432,7 @@
           <t>(11,23)</t>
         </is>
       </c>
+      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10950,6 +11467,7 @@
           <t>(11,24)</t>
         </is>
       </c>
+      <c r="J298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10984,6 +11502,7 @@
           <t>(12,13)</t>
         </is>
       </c>
+      <c r="J299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11018,6 +11537,7 @@
           <t>(12,14)</t>
         </is>
       </c>
+      <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11052,6 +11572,7 @@
           <t>(12,15)</t>
         </is>
       </c>
+      <c r="J301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11086,6 +11607,7 @@
           <t>(12,19)</t>
         </is>
       </c>
+      <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11120,6 +11642,7 @@
           <t>(12,20)</t>
         </is>
       </c>
+      <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11154,6 +11677,7 @@
           <t>(12,21)</t>
         </is>
       </c>
+      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11188,6 +11712,7 @@
           <t>(12,22)</t>
         </is>
       </c>
+      <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11222,6 +11747,7 @@
           <t>(12,23)</t>
         </is>
       </c>
+      <c r="J306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11256,6 +11782,7 @@
           <t>(12,24)</t>
         </is>
       </c>
+      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11290,6 +11817,7 @@
           <t>(13,14)</t>
         </is>
       </c>
+      <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11324,6 +11852,7 @@
           <t>(13,15)</t>
         </is>
       </c>
+      <c r="J309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11358,6 +11887,7 @@
           <t>(13,19)</t>
         </is>
       </c>
+      <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11392,6 +11922,7 @@
           <t>(13,20)</t>
         </is>
       </c>
+      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11426,6 +11957,7 @@
           <t>(13,21)</t>
         </is>
       </c>
+      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11460,6 +11992,7 @@
           <t>(13,22)</t>
         </is>
       </c>
+      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11494,6 +12027,7 @@
           <t>(13,23)</t>
         </is>
       </c>
+      <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11528,6 +12062,7 @@
           <t>(13,24)</t>
         </is>
       </c>
+      <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11562,6 +12097,7 @@
           <t>(14,15)</t>
         </is>
       </c>
+      <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11596,6 +12132,7 @@
           <t>(14,19)</t>
         </is>
       </c>
+      <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11630,6 +12167,7 @@
           <t>(14,20)</t>
         </is>
       </c>
+      <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11664,6 +12202,7 @@
           <t>(14,21)</t>
         </is>
       </c>
+      <c r="J319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11698,6 +12237,7 @@
           <t>(14,22)</t>
         </is>
       </c>
+      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11732,6 +12272,7 @@
           <t>(14,23)</t>
         </is>
       </c>
+      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11766,6 +12307,7 @@
           <t>(14,24)</t>
         </is>
       </c>
+      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11800,6 +12342,7 @@
           <t>(15,19)</t>
         </is>
       </c>
+      <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11834,6 +12377,7 @@
           <t>(15,20)</t>
         </is>
       </c>
+      <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11868,6 +12412,7 @@
           <t>(15,21)</t>
         </is>
       </c>
+      <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11902,6 +12447,7 @@
           <t>(15,22)</t>
         </is>
       </c>
+      <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11936,6 +12482,7 @@
           <t>(15,23)</t>
         </is>
       </c>
+      <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11970,6 +12517,7 @@
           <t>(15,24)</t>
         </is>
       </c>
+      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12004,6 +12552,7 @@
           <t>(19,20)</t>
         </is>
       </c>
+      <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12038,6 +12587,7 @@
           <t>(19,21)</t>
         </is>
       </c>
+      <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12072,6 +12622,7 @@
           <t>(19,22)</t>
         </is>
       </c>
+      <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12106,6 +12657,7 @@
           <t>(19,23)</t>
         </is>
       </c>
+      <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12140,6 +12692,7 @@
           <t>(19,24)</t>
         </is>
       </c>
+      <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12174,6 +12727,7 @@
           <t>(20,21)</t>
         </is>
       </c>
+      <c r="J334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12208,6 +12762,7 @@
           <t>(20,22)</t>
         </is>
       </c>
+      <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12242,6 +12797,7 @@
           <t>(20,23)</t>
         </is>
       </c>
+      <c r="J336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12276,6 +12832,7 @@
           <t>(20,24)</t>
         </is>
       </c>
+      <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12310,6 +12867,7 @@
           <t>(21,22)</t>
         </is>
       </c>
+      <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12344,6 +12902,7 @@
           <t>(21,23)</t>
         </is>
       </c>
+      <c r="J339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12378,6 +12937,7 @@
           <t>(21,24)</t>
         </is>
       </c>
+      <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12412,6 +12972,7 @@
           <t>(22,23)</t>
         </is>
       </c>
+      <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12446,6 +13007,7 @@
           <t>(22,24)</t>
         </is>
       </c>
+      <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12480,6 +13042,7 @@
           <t>(23,24)</t>
         </is>
       </c>
+      <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12514,6 +13077,7 @@
           <t>(7,8)</t>
         </is>
       </c>
+      <c r="J344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12548,6 +13112,7 @@
           <t>(7,9)</t>
         </is>
       </c>
+      <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12582,6 +13147,7 @@
           <t>(7,16)</t>
         </is>
       </c>
+      <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12616,6 +13182,7 @@
           <t>(7,17)</t>
         </is>
       </c>
+      <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12650,6 +13217,7 @@
           <t>(7,18)</t>
         </is>
       </c>
+      <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12684,6 +13252,7 @@
           <t>(7,25)</t>
         </is>
       </c>
+      <c r="J349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12718,6 +13287,7 @@
           <t>(7,26)</t>
         </is>
       </c>
+      <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12752,6 +13322,7 @@
           <t>(7,27)</t>
         </is>
       </c>
+      <c r="J351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12786,6 +13357,7 @@
           <t>(8,9)</t>
         </is>
       </c>
+      <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12820,6 +13392,7 @@
           <t>(8,16)</t>
         </is>
       </c>
+      <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12854,6 +13427,7 @@
           <t>(8,17)</t>
         </is>
       </c>
+      <c r="J354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12888,6 +13462,7 @@
           <t>(8,18)</t>
         </is>
       </c>
+      <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12922,6 +13497,7 @@
           <t>(8,25)</t>
         </is>
       </c>
+      <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12956,6 +13532,7 @@
           <t>(8,26)</t>
         </is>
       </c>
+      <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12990,6 +13567,7 @@
           <t>(8,27)</t>
         </is>
       </c>
+      <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13024,6 +13602,7 @@
           <t>(9,16)</t>
         </is>
       </c>
+      <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13058,6 +13637,7 @@
           <t>(9,17)</t>
         </is>
       </c>
+      <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13092,6 +13672,7 @@
           <t>(9,18)</t>
         </is>
       </c>
+      <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13126,6 +13707,7 @@
           <t>(9,25)</t>
         </is>
       </c>
+      <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -13160,6 +13742,7 @@
           <t>(9,26)</t>
         </is>
       </c>
+      <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -13194,6 +13777,7 @@
           <t>(9,27)</t>
         </is>
       </c>
+      <c r="J364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13228,6 +13812,7 @@
           <t>(16,17)</t>
         </is>
       </c>
+      <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13262,6 +13847,7 @@
           <t>(16,18)</t>
         </is>
       </c>
+      <c r="J366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13296,6 +13882,7 @@
           <t>(16,25)</t>
         </is>
       </c>
+      <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13330,6 +13917,7 @@
           <t>(16,26)</t>
         </is>
       </c>
+      <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13364,6 +13952,7 @@
           <t>(16,27)</t>
         </is>
       </c>
+      <c r="J369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13398,6 +13987,7 @@
           <t>(17,18)</t>
         </is>
       </c>
+      <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13432,6 +14022,7 @@
           <t>(17,25)</t>
         </is>
       </c>
+      <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13466,6 +14057,7 @@
           <t>(17,26)</t>
         </is>
       </c>
+      <c r="J372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13500,6 +14092,7 @@
           <t>(17,27)</t>
         </is>
       </c>
+      <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13534,6 +14127,7 @@
           <t>(18,25)</t>
         </is>
       </c>
+      <c r="J374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13568,6 +14162,7 @@
           <t>(18,26)</t>
         </is>
       </c>
+      <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13602,6 +14197,7 @@
           <t>(18,27)</t>
         </is>
       </c>
+      <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13636,6 +14232,7 @@
           <t>(25,26)</t>
         </is>
       </c>
+      <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13670,6 +14267,7 @@
           <t>(25,27)</t>
         </is>
       </c>
+      <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13704,6 +14302,7 @@
           <t>(26,27)</t>
         </is>
       </c>
+      <c r="J379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13734,6 +14333,7 @@
           <t>(1,2)</t>
         </is>
       </c>
+      <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13764,6 +14364,7 @@
           <t>(1,3)</t>
         </is>
       </c>
+      <c r="J381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13794,6 +14395,7 @@
           <t>(1,4)</t>
         </is>
       </c>
+      <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13824,6 +14426,7 @@
           <t>(1,5)</t>
         </is>
       </c>
+      <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13854,6 +14457,7 @@
           <t>(1,6)</t>
         </is>
       </c>
+      <c r="J384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13884,6 +14488,7 @@
           <t>(1,7)</t>
         </is>
       </c>
+      <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13914,6 +14519,7 @@
           <t>(1,8)</t>
         </is>
       </c>
+      <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13944,6 +14550,7 @@
           <t>(1,9)</t>
         </is>
       </c>
+      <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13974,6 +14581,7 @@
           <t>(1,10)</t>
         </is>
       </c>
+      <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14004,6 +14612,7 @@
           <t>(1,11)</t>
         </is>
       </c>
+      <c r="J389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14034,6 +14643,7 @@
           <t>(1,12)</t>
         </is>
       </c>
+      <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14064,6 +14674,7 @@
           <t>(1,13)</t>
         </is>
       </c>
+      <c r="J391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -14094,6 +14705,7 @@
           <t>(1,14)</t>
         </is>
       </c>
+      <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14124,6 +14736,7 @@
           <t>(1,15)</t>
         </is>
       </c>
+      <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14154,6 +14767,7 @@
           <t>(1,16)</t>
         </is>
       </c>
+      <c r="J394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -14184,6 +14798,7 @@
           <t>(1,17)</t>
         </is>
       </c>
+      <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14214,6 +14829,7 @@
           <t>(1,18)</t>
         </is>
       </c>
+      <c r="J396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14244,6 +14860,7 @@
           <t>(1,19)</t>
         </is>
       </c>
+      <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14274,6 +14891,7 @@
           <t>(1,20)</t>
         </is>
       </c>
+      <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14304,6 +14922,7 @@
           <t>(1,21)</t>
         </is>
       </c>
+      <c r="J399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14334,6 +14953,7 @@
           <t>(1,22)</t>
         </is>
       </c>
+      <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14364,6 +14984,7 @@
           <t>(1,23)</t>
         </is>
       </c>
+      <c r="J401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14394,6 +15015,7 @@
           <t>(1,24)</t>
         </is>
       </c>
+      <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14424,6 +15046,7 @@
           <t>(1,25)</t>
         </is>
       </c>
+      <c r="J403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14454,6 +15077,7 @@
           <t>(1,26)</t>
         </is>
       </c>
+      <c r="J404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14484,6 +15108,7 @@
           <t>(1,27)</t>
         </is>
       </c>
+      <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14514,6 +15139,7 @@
           <t>(2,3)</t>
         </is>
       </c>
+      <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14544,6 +15170,7 @@
           <t>(2,4)</t>
         </is>
       </c>
+      <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14574,6 +15201,7 @@
           <t>(2,5)</t>
         </is>
       </c>
+      <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14604,6 +15232,7 @@
           <t>(2,6)</t>
         </is>
       </c>
+      <c r="J409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14634,6 +15263,7 @@
           <t>(2,7)</t>
         </is>
       </c>
+      <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14664,6 +15294,7 @@
           <t>(2,8)</t>
         </is>
       </c>
+      <c r="J411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14694,6 +15325,7 @@
           <t>(2,9)</t>
         </is>
       </c>
+      <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14724,6 +15356,7 @@
           <t>(2,10)</t>
         </is>
       </c>
+      <c r="J413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14754,6 +15387,7 @@
           <t>(2,11)</t>
         </is>
       </c>
+      <c r="J414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14784,6 +15418,7 @@
           <t>(2,12)</t>
         </is>
       </c>
+      <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14814,6 +15449,7 @@
           <t>(2,13)</t>
         </is>
       </c>
+      <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14844,6 +15480,7 @@
           <t>(2,14)</t>
         </is>
       </c>
+      <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14874,6 +15511,7 @@
           <t>(2,15)</t>
         </is>
       </c>
+      <c r="J418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14904,6 +15542,7 @@
           <t>(2,16)</t>
         </is>
       </c>
+      <c r="J419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14934,6 +15573,7 @@
           <t>(2,17)</t>
         </is>
       </c>
+      <c r="J420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14964,6 +15604,7 @@
           <t>(2,18)</t>
         </is>
       </c>
+      <c r="J421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14994,6 +15635,7 @@
           <t>(2,19)</t>
         </is>
       </c>
+      <c r="J422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -15024,6 +15666,7 @@
           <t>(2,20)</t>
         </is>
       </c>
+      <c r="J423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -15054,6 +15697,7 @@
           <t>(2,21)</t>
         </is>
       </c>
+      <c r="J424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15084,6 +15728,7 @@
           <t>(2,22)</t>
         </is>
       </c>
+      <c r="J425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15114,6 +15759,7 @@
           <t>(2,23)</t>
         </is>
       </c>
+      <c r="J426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15144,6 +15790,7 @@
           <t>(2,24)</t>
         </is>
       </c>
+      <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15174,6 +15821,7 @@
           <t>(2,25)</t>
         </is>
       </c>
+      <c r="J428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15204,6 +15852,7 @@
           <t>(2,26)</t>
         </is>
       </c>
+      <c r="J429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15234,6 +15883,7 @@
           <t>(2,27)</t>
         </is>
       </c>
+      <c r="J430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15264,6 +15914,7 @@
           <t>(3,4)</t>
         </is>
       </c>
+      <c r="J431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15294,6 +15945,7 @@
           <t>(3,5)</t>
         </is>
       </c>
+      <c r="J432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15324,6 +15976,7 @@
           <t>(3,6)</t>
         </is>
       </c>
+      <c r="J433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15354,6 +16007,7 @@
           <t>(3,7)</t>
         </is>
       </c>
+      <c r="J434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15384,6 +16038,7 @@
           <t>(3,8)</t>
         </is>
       </c>
+      <c r="J435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15414,6 +16069,7 @@
           <t>(3,9)</t>
         </is>
       </c>
+      <c r="J436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15444,6 +16100,7 @@
           <t>(3,10)</t>
         </is>
       </c>
+      <c r="J437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15474,6 +16131,7 @@
           <t>(3,11)</t>
         </is>
       </c>
+      <c r="J438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15504,6 +16162,7 @@
           <t>(3,12)</t>
         </is>
       </c>
+      <c r="J439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15534,6 +16193,7 @@
           <t>(3,13)</t>
         </is>
       </c>
+      <c r="J440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15564,6 +16224,7 @@
           <t>(3,14)</t>
         </is>
       </c>
+      <c r="J441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15594,6 +16255,7 @@
           <t>(3,15)</t>
         </is>
       </c>
+      <c r="J442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15624,6 +16286,7 @@
           <t>(3,16)</t>
         </is>
       </c>
+      <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15654,6 +16317,7 @@
           <t>(3,17)</t>
         </is>
       </c>
+      <c r="J444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15684,6 +16348,7 @@
           <t>(3,18)</t>
         </is>
       </c>
+      <c r="J445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15714,6 +16379,7 @@
           <t>(3,19)</t>
         </is>
       </c>
+      <c r="J446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15744,6 +16410,7 @@
           <t>(3,20)</t>
         </is>
       </c>
+      <c r="J447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15774,6 +16441,7 @@
           <t>(3,21)</t>
         </is>
       </c>
+      <c r="J448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -15804,6 +16472,7 @@
           <t>(3,22)</t>
         </is>
       </c>
+      <c r="J449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -15834,6 +16503,7 @@
           <t>(3,23)</t>
         </is>
       </c>
+      <c r="J450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -15864,6 +16534,7 @@
           <t>(3,24)</t>
         </is>
       </c>
+      <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -15894,6 +16565,7 @@
           <t>(3,25)</t>
         </is>
       </c>
+      <c r="J452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -15924,6 +16596,7 @@
           <t>(3,26)</t>
         </is>
       </c>
+      <c r="J453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -15954,6 +16627,7 @@
           <t>(3,27)</t>
         </is>
       </c>
+      <c r="J454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -15984,6 +16658,7 @@
           <t>(4,5)</t>
         </is>
       </c>
+      <c r="J455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16014,6 +16689,7 @@
           <t>(4,6)</t>
         </is>
       </c>
+      <c r="J456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16044,6 +16720,7 @@
           <t>(4,7)</t>
         </is>
       </c>
+      <c r="J457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16074,6 +16751,7 @@
           <t>(4,8)</t>
         </is>
       </c>
+      <c r="J458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16104,6 +16782,7 @@
           <t>(4,9)</t>
         </is>
       </c>
+      <c r="J459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16134,6 +16813,7 @@
           <t>(4,10)</t>
         </is>
       </c>
+      <c r="J460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16164,6 +16844,7 @@
           <t>(4,11)</t>
         </is>
       </c>
+      <c r="J461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -16194,6 +16875,7 @@
           <t>(4,12)</t>
         </is>
       </c>
+      <c r="J462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -16224,6 +16906,7 @@
           <t>(4,13)</t>
         </is>
       </c>
+      <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16254,6 +16937,7 @@
           <t>(4,14)</t>
         </is>
       </c>
+      <c r="J464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16284,6 +16968,7 @@
           <t>(4,15)</t>
         </is>
       </c>
+      <c r="J465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16314,6 +16999,7 @@
           <t>(4,16)</t>
         </is>
       </c>
+      <c r="J466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16344,6 +17030,7 @@
           <t>(4,17)</t>
         </is>
       </c>
+      <c r="J467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16374,6 +17061,7 @@
           <t>(4,18)</t>
         </is>
       </c>
+      <c r="J468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16404,6 +17092,7 @@
           <t>(4,19)</t>
         </is>
       </c>
+      <c r="J469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16434,6 +17123,7 @@
           <t>(4,20)</t>
         </is>
       </c>
+      <c r="J470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16464,6 +17154,7 @@
           <t>(4,21)</t>
         </is>
       </c>
+      <c r="J471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16494,6 +17185,7 @@
           <t>(4,22)</t>
         </is>
       </c>
+      <c r="J472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16524,6 +17216,7 @@
           <t>(4,23)</t>
         </is>
       </c>
+      <c r="J473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16554,6 +17247,7 @@
           <t>(4,24)</t>
         </is>
       </c>
+      <c r="J474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16584,6 +17278,7 @@
           <t>(4,25)</t>
         </is>
       </c>
+      <c r="J475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16614,6 +17309,7 @@
           <t>(4,26)</t>
         </is>
       </c>
+      <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16644,6 +17340,7 @@
           <t>(4,27)</t>
         </is>
       </c>
+      <c r="J477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16674,6 +17371,7 @@
           <t>(5,6)</t>
         </is>
       </c>
+      <c r="J478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16704,6 +17402,7 @@
           <t>(5,7)</t>
         </is>
       </c>
+      <c r="J479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16734,6 +17433,7 @@
           <t>(5,8)</t>
         </is>
       </c>
+      <c r="J480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16764,6 +17464,7 @@
           <t>(5,9)</t>
         </is>
       </c>
+      <c r="J481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -16794,6 +17495,7 @@
           <t>(5,10)</t>
         </is>
       </c>
+      <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -16824,6 +17526,7 @@
           <t>(5,11)</t>
         </is>
       </c>
+      <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -16854,6 +17557,7 @@
           <t>(5,12)</t>
         </is>
       </c>
+      <c r="J484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -16884,6 +17588,7 @@
           <t>(5,13)</t>
         </is>
       </c>
+      <c r="J485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -16914,6 +17619,7 @@
           <t>(5,14)</t>
         </is>
       </c>
+      <c r="J486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -16944,6 +17650,7 @@
           <t>(5,15)</t>
         </is>
       </c>
+      <c r="J487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -16974,6 +17681,7 @@
           <t>(5,16)</t>
         </is>
       </c>
+      <c r="J488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17004,6 +17712,7 @@
           <t>(5,17)</t>
         </is>
       </c>
+      <c r="J489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -17034,6 +17743,7 @@
           <t>(5,18)</t>
         </is>
       </c>
+      <c r="J490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -17064,6 +17774,7 @@
           <t>(5,19)</t>
         </is>
       </c>
+      <c r="J491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -17094,6 +17805,7 @@
           <t>(5,20)</t>
         </is>
       </c>
+      <c r="J492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -17124,6 +17836,7 @@
           <t>(5,21)</t>
         </is>
       </c>
+      <c r="J493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17154,6 +17867,7 @@
           <t>(5,22)</t>
         </is>
       </c>
+      <c r="J494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -17184,6 +17898,7 @@
           <t>(5,23)</t>
         </is>
       </c>
+      <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17214,6 +17929,7 @@
           <t>(5,24)</t>
         </is>
       </c>
+      <c r="J496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17244,6 +17960,7 @@
           <t>(5,25)</t>
         </is>
       </c>
+      <c r="J497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17274,6 +17991,7 @@
           <t>(5,26)</t>
         </is>
       </c>
+      <c r="J498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17304,6 +18022,7 @@
           <t>(5,27)</t>
         </is>
       </c>
+      <c r="J499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17334,6 +18053,7 @@
           <t>(6,7)</t>
         </is>
       </c>
+      <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17364,6 +18084,7 @@
           <t>(6,8)</t>
         </is>
       </c>
+      <c r="J501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17394,6 +18115,7 @@
           <t>(6,9)</t>
         </is>
       </c>
+      <c r="J502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17424,6 +18146,7 @@
           <t>(6,10)</t>
         </is>
       </c>
+      <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17454,6 +18177,7 @@
           <t>(6,11)</t>
         </is>
       </c>
+      <c r="J504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17484,6 +18208,7 @@
           <t>(6,12)</t>
         </is>
       </c>
+      <c r="J505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17514,6 +18239,7 @@
           <t>(6,13)</t>
         </is>
       </c>
+      <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17544,6 +18270,7 @@
           <t>(6,14)</t>
         </is>
       </c>
+      <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17574,6 +18301,7 @@
           <t>(6,15)</t>
         </is>
       </c>
+      <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17604,6 +18332,7 @@
           <t>(6,16)</t>
         </is>
       </c>
+      <c r="J509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -17634,6 +18363,7 @@
           <t>(6,17)</t>
         </is>
       </c>
+      <c r="J510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17664,6 +18394,7 @@
           <t>(6,18)</t>
         </is>
       </c>
+      <c r="J511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17694,6 +18425,7 @@
           <t>(6,19)</t>
         </is>
       </c>
+      <c r="J512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17724,6 +18456,7 @@
           <t>(6,20)</t>
         </is>
       </c>
+      <c r="J513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17754,6 +18487,7 @@
           <t>(6,21)</t>
         </is>
       </c>
+      <c r="J514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -17784,6 +18518,7 @@
           <t>(6,22)</t>
         </is>
       </c>
+      <c r="J515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -17814,6 +18549,7 @@
           <t>(6,23)</t>
         </is>
       </c>
+      <c r="J516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -17844,6 +18580,7 @@
           <t>(6,24)</t>
         </is>
       </c>
+      <c r="J517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -17874,6 +18611,7 @@
           <t>(6,25)</t>
         </is>
       </c>
+      <c r="J518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -17904,6 +18642,7 @@
           <t>(6,26)</t>
         </is>
       </c>
+      <c r="J519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -17934,6 +18673,7 @@
           <t>(6,27)</t>
         </is>
       </c>
+      <c r="J520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -17964,6 +18704,7 @@
           <t>(7,8)</t>
         </is>
       </c>
+      <c r="J521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -17994,6 +18735,7 @@
           <t>(7,9)</t>
         </is>
       </c>
+      <c r="J522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -18024,6 +18766,7 @@
           <t>(7,10)</t>
         </is>
       </c>
+      <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -18054,6 +18797,7 @@
           <t>(7,11)</t>
         </is>
       </c>
+      <c r="J524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -18084,6 +18828,7 @@
           <t>(7,12)</t>
         </is>
       </c>
+      <c r="J525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18114,6 +18859,7 @@
           <t>(7,13)</t>
         </is>
       </c>
+      <c r="J526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18144,6 +18890,7 @@
           <t>(7,14)</t>
         </is>
       </c>
+      <c r="J527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -18174,6 +18921,7 @@
           <t>(7,15)</t>
         </is>
       </c>
+      <c r="J528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -18204,6 +18952,7 @@
           <t>(7,16)</t>
         </is>
       </c>
+      <c r="J529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -18234,6 +18983,7 @@
           <t>(7,17)</t>
         </is>
       </c>
+      <c r="J530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -18264,6 +19014,7 @@
           <t>(7,18)</t>
         </is>
       </c>
+      <c r="J531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -18294,6 +19045,7 @@
           <t>(7,19)</t>
         </is>
       </c>
+      <c r="J532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -18324,6 +19076,7 @@
           <t>(7,20)</t>
         </is>
       </c>
+      <c r="J533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -18354,6 +19107,7 @@
           <t>(7,21)</t>
         </is>
       </c>
+      <c r="J534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18384,6 +19138,7 @@
           <t>(7,22)</t>
         </is>
       </c>
+      <c r="J535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18414,6 +19169,7 @@
           <t>(7,23)</t>
         </is>
       </c>
+      <c r="J536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18444,6 +19200,7 @@
           <t>(7,24)</t>
         </is>
       </c>
+      <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -18474,6 +19231,7 @@
           <t>(7,25)</t>
         </is>
       </c>
+      <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18504,6 +19262,7 @@
           <t>(7,26)</t>
         </is>
       </c>
+      <c r="J539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18534,6 +19293,7 @@
           <t>(7,27)</t>
         </is>
       </c>
+      <c r="J540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18564,6 +19324,7 @@
           <t>(8,9)</t>
         </is>
       </c>
+      <c r="J541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18594,6 +19355,7 @@
           <t>(8,10)</t>
         </is>
       </c>
+      <c r="J542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18624,6 +19386,7 @@
           <t>(8,11)</t>
         </is>
       </c>
+      <c r="J543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -18654,6 +19417,7 @@
           <t>(8,12)</t>
         </is>
       </c>
+      <c r="J544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -18684,6 +19448,7 @@
           <t>(8,13)</t>
         </is>
       </c>
+      <c r="J545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -18714,6 +19479,7 @@
           <t>(8,14)</t>
         </is>
       </c>
+      <c r="J546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -18744,6 +19510,7 @@
           <t>(8,15)</t>
         </is>
       </c>
+      <c r="J547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -18774,6 +19541,7 @@
           <t>(8,16)</t>
         </is>
       </c>
+      <c r="J548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -18804,6 +19572,7 @@
           <t>(8,17)</t>
         </is>
       </c>
+      <c r="J549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -18834,6 +19603,7 @@
           <t>(8,18)</t>
         </is>
       </c>
+      <c r="J550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -18864,6 +19634,7 @@
           <t>(8,19)</t>
         </is>
       </c>
+      <c r="J551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -18894,6 +19665,7 @@
           <t>(8,20)</t>
         </is>
       </c>
+      <c r="J552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -18924,6 +19696,7 @@
           <t>(8,21)</t>
         </is>
       </c>
+      <c r="J553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -18954,6 +19727,7 @@
           <t>(8,22)</t>
         </is>
       </c>
+      <c r="J554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -18984,6 +19758,7 @@
           <t>(8,23)</t>
         </is>
       </c>
+      <c r="J555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -19014,6 +19789,7 @@
           <t>(8,24)</t>
         </is>
       </c>
+      <c r="J556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -19044,6 +19820,7 @@
           <t>(8,25)</t>
         </is>
       </c>
+      <c r="J557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -19074,6 +19851,7 @@
           <t>(8,26)</t>
         </is>
       </c>
+      <c r="J558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -19104,6 +19882,7 @@
           <t>(8,27)</t>
         </is>
       </c>
+      <c r="J559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -19134,6 +19913,7 @@
           <t>(9,10)</t>
         </is>
       </c>
+      <c r="J560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -19164,6 +19944,7 @@
           <t>(9,11)</t>
         </is>
       </c>
+      <c r="J561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -19194,6 +19975,7 @@
           <t>(9,12)</t>
         </is>
       </c>
+      <c r="J562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -19224,6 +20006,7 @@
           <t>(9,13)</t>
         </is>
       </c>
+      <c r="J563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -19254,6 +20037,7 @@
           <t>(9,14)</t>
         </is>
       </c>
+      <c r="J564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -19284,6 +20068,7 @@
           <t>(9,15)</t>
         </is>
       </c>
+      <c r="J565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -19314,6 +20099,7 @@
           <t>(9,16)</t>
         </is>
       </c>
+      <c r="J566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -19344,6 +20130,7 @@
           <t>(9,17)</t>
         </is>
       </c>
+      <c r="J567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -19374,6 +20161,7 @@
           <t>(9,18)</t>
         </is>
       </c>
+      <c r="J568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -19404,6 +20192,7 @@
           <t>(9,19)</t>
         </is>
       </c>
+      <c r="J569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -19434,6 +20223,7 @@
           <t>(9,20)</t>
         </is>
       </c>
+      <c r="J570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -19464,6 +20254,7 @@
           <t>(9,21)</t>
         </is>
       </c>
+      <c r="J571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -19494,6 +20285,7 @@
           <t>(9,22)</t>
         </is>
       </c>
+      <c r="J572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -19524,6 +20316,7 @@
           <t>(9,23)</t>
         </is>
       </c>
+      <c r="J573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -19554,6 +20347,7 @@
           <t>(9,24)</t>
         </is>
       </c>
+      <c r="J574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -19584,6 +20378,7 @@
           <t>(9,25)</t>
         </is>
       </c>
+      <c r="J575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -19614,6 +20409,7 @@
           <t>(9,26)</t>
         </is>
       </c>
+      <c r="J576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -19644,6 +20440,7 @@
           <t>(9,27)</t>
         </is>
       </c>
+      <c r="J577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -19674,6 +20471,7 @@
           <t>(10,11)</t>
         </is>
       </c>
+      <c r="J578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -19704,6 +20502,7 @@
           <t>(10,12)</t>
         </is>
       </c>
+      <c r="J579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -19734,6 +20533,7 @@
           <t>(10,13)</t>
         </is>
       </c>
+      <c r="J580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -19764,6 +20564,7 @@
           <t>(10,14)</t>
         </is>
       </c>
+      <c r="J581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -19794,6 +20595,7 @@
           <t>(10,15)</t>
         </is>
       </c>
+      <c r="J582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -19824,6 +20626,7 @@
           <t>(10,16)</t>
         </is>
       </c>
+      <c r="J583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -19854,6 +20657,7 @@
           <t>(10,17)</t>
         </is>
       </c>
+      <c r="J584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -19884,6 +20688,7 @@
           <t>(10,18)</t>
         </is>
       </c>
+      <c r="J585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -19914,6 +20719,7 @@
           <t>(10,19)</t>
         </is>
       </c>
+      <c r="J586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -19944,6 +20750,7 @@
           <t>(10,20)</t>
         </is>
       </c>
+      <c r="J587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -19974,6 +20781,7 @@
           <t>(10,21)</t>
         </is>
       </c>
+      <c r="J588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -20004,6 +20812,7 @@
           <t>(10,22)</t>
         </is>
       </c>
+      <c r="J589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -20034,6 +20843,7 @@
           <t>(10,23)</t>
         </is>
       </c>
+      <c r="J590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -20064,6 +20874,7 @@
           <t>(10,24)</t>
         </is>
       </c>
+      <c r="J591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -20094,6 +20905,7 @@
           <t>(10,25)</t>
         </is>
       </c>
+      <c r="J592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -20124,6 +20936,7 @@
           <t>(10,26)</t>
         </is>
       </c>
+      <c r="J593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -20154,6 +20967,7 @@
           <t>(10,27)</t>
         </is>
       </c>
+      <c r="J594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -20184,6 +20998,7 @@
           <t>(11,12)</t>
         </is>
       </c>
+      <c r="J595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -20214,6 +21029,7 @@
           <t>(11,13)</t>
         </is>
       </c>
+      <c r="J596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -20244,6 +21060,7 @@
           <t>(11,14)</t>
         </is>
       </c>
+      <c r="J597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -20274,6 +21091,7 @@
           <t>(11,15)</t>
         </is>
       </c>
+      <c r="J598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -20304,6 +21122,7 @@
           <t>(11,16)</t>
         </is>
       </c>
+      <c r="J599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -20334,6 +21153,7 @@
           <t>(11,17)</t>
         </is>
       </c>
+      <c r="J600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -20364,6 +21184,7 @@
           <t>(11,18)</t>
         </is>
       </c>
+      <c r="J601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -20394,6 +21215,7 @@
           <t>(11,19)</t>
         </is>
       </c>
+      <c r="J602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -20424,6 +21246,7 @@
           <t>(11,20)</t>
         </is>
       </c>
+      <c r="J603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -20454,6 +21277,7 @@
           <t>(11,21)</t>
         </is>
       </c>
+      <c r="J604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -20484,6 +21308,7 @@
           <t>(11,22)</t>
         </is>
       </c>
+      <c r="J605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -20514,6 +21339,7 @@
           <t>(11,23)</t>
         </is>
       </c>
+      <c r="J606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -20544,6 +21370,7 @@
           <t>(11,24)</t>
         </is>
       </c>
+      <c r="J607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -20574,6 +21401,7 @@
           <t>(11,25)</t>
         </is>
       </c>
+      <c r="J608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -20604,6 +21432,7 @@
           <t>(11,26)</t>
         </is>
       </c>
+      <c r="J609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -20634,6 +21463,7 @@
           <t>(11,27)</t>
         </is>
       </c>
+      <c r="J610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -20664,6 +21494,7 @@
           <t>(12,13)</t>
         </is>
       </c>
+      <c r="J611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -20694,6 +21525,7 @@
           <t>(12,14)</t>
         </is>
       </c>
+      <c r="J612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -20724,6 +21556,7 @@
           <t>(12,15)</t>
         </is>
       </c>
+      <c r="J613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -20754,6 +21587,7 @@
           <t>(12,16)</t>
         </is>
       </c>
+      <c r="J614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -20784,6 +21618,7 @@
           <t>(12,17)</t>
         </is>
       </c>
+      <c r="J615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -20814,6 +21649,7 @@
           <t>(12,18)</t>
         </is>
       </c>
+      <c r="J616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -20844,6 +21680,7 @@
           <t>(12,19)</t>
         </is>
       </c>
+      <c r="J617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -20874,6 +21711,7 @@
           <t>(12,20)</t>
         </is>
       </c>
+      <c r="J618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -20904,6 +21742,7 @@
           <t>(12,21)</t>
         </is>
       </c>
+      <c r="J619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -20934,6 +21773,7 @@
           <t>(12,22)</t>
         </is>
       </c>
+      <c r="J620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -20964,6 +21804,7 @@
           <t>(12,23)</t>
         </is>
       </c>
+      <c r="J621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -20994,6 +21835,7 @@
           <t>(12,24)</t>
         </is>
       </c>
+      <c r="J622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -21024,6 +21866,7 @@
           <t>(12,25)</t>
         </is>
       </c>
+      <c r="J623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -21054,6 +21897,7 @@
           <t>(12,26)</t>
         </is>
       </c>
+      <c r="J624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -21084,6 +21928,7 @@
           <t>(12,27)</t>
         </is>
       </c>
+      <c r="J625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -21114,6 +21959,7 @@
           <t>(13,14)</t>
         </is>
       </c>
+      <c r="J626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -21144,6 +21990,7 @@
           <t>(13,15)</t>
         </is>
       </c>
+      <c r="J627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -21174,6 +22021,7 @@
           <t>(13,16)</t>
         </is>
       </c>
+      <c r="J628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -21204,6 +22052,7 @@
           <t>(13,17)</t>
         </is>
       </c>
+      <c r="J629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -21234,6 +22083,7 @@
           <t>(13,18)</t>
         </is>
       </c>
+      <c r="J630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -21264,6 +22114,7 @@
           <t>(13,19)</t>
         </is>
       </c>
+      <c r="J631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -21294,6 +22145,7 @@
           <t>(13,20)</t>
         </is>
       </c>
+      <c r="J632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -21324,6 +22176,7 @@
           <t>(13,21)</t>
         </is>
       </c>
+      <c r="J633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -21354,6 +22207,7 @@
           <t>(13,22)</t>
         </is>
       </c>
+      <c r="J634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -21384,6 +22238,7 @@
           <t>(13,23)</t>
         </is>
       </c>
+      <c r="J635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -21414,6 +22269,7 @@
           <t>(13,24)</t>
         </is>
       </c>
+      <c r="J636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -21444,6 +22300,7 @@
           <t>(13,25)</t>
         </is>
       </c>
+      <c r="J637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -21474,6 +22331,7 @@
           <t>(13,26)</t>
         </is>
       </c>
+      <c r="J638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -21504,6 +22362,7 @@
           <t>(13,27)</t>
         </is>
       </c>
+      <c r="J639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -21534,6 +22393,7 @@
           <t>(14,15)</t>
         </is>
       </c>
+      <c r="J640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -21564,6 +22424,7 @@
           <t>(14,16)</t>
         </is>
       </c>
+      <c r="J641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -21594,6 +22455,7 @@
           <t>(14,17)</t>
         </is>
       </c>
+      <c r="J642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -21624,6 +22486,7 @@
           <t>(14,18)</t>
         </is>
       </c>
+      <c r="J643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -21654,6 +22517,7 @@
           <t>(14,19)</t>
         </is>
       </c>
+      <c r="J644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -21684,6 +22548,7 @@
           <t>(14,20)</t>
         </is>
       </c>
+      <c r="J645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -21714,6 +22579,7 @@
           <t>(14,21)</t>
         </is>
       </c>
+      <c r="J646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -21744,6 +22610,7 @@
           <t>(14,22)</t>
         </is>
       </c>
+      <c r="J647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -21774,6 +22641,7 @@
           <t>(14,23)</t>
         </is>
       </c>
+      <c r="J648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -21804,6 +22672,7 @@
           <t>(14,24)</t>
         </is>
       </c>
+      <c r="J649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -21834,6 +22703,7 @@
           <t>(14,25)</t>
         </is>
       </c>
+      <c r="J650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -21864,6 +22734,7 @@
           <t>(14,26)</t>
         </is>
       </c>
+      <c r="J651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -21894,6 +22765,7 @@
           <t>(14,27)</t>
         </is>
       </c>
+      <c r="J652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -21924,6 +22796,7 @@
           <t>(15,16)</t>
         </is>
       </c>
+      <c r="J653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -21954,6 +22827,7 @@
           <t>(15,17)</t>
         </is>
       </c>
+      <c r="J654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -21984,6 +22858,7 @@
           <t>(15,18)</t>
         </is>
       </c>
+      <c r="J655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -22014,6 +22889,7 @@
           <t>(15,19)</t>
         </is>
       </c>
+      <c r="J656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -22044,6 +22920,7 @@
           <t>(15,20)</t>
         </is>
       </c>
+      <c r="J657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -22074,6 +22951,7 @@
           <t>(15,21)</t>
         </is>
       </c>
+      <c r="J658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -22104,6 +22982,7 @@
           <t>(15,22)</t>
         </is>
       </c>
+      <c r="J659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -22134,6 +23013,7 @@
           <t>(15,23)</t>
         </is>
       </c>
+      <c r="J660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -22164,6 +23044,7 @@
           <t>(15,24)</t>
         </is>
       </c>
+      <c r="J661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -22194,6 +23075,7 @@
           <t>(15,25)</t>
         </is>
       </c>
+      <c r="J662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -22224,6 +23106,7 @@
           <t>(15,26)</t>
         </is>
       </c>
+      <c r="J663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -22254,6 +23137,7 @@
           <t>(15,27)</t>
         </is>
       </c>
+      <c r="J664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -22284,6 +23168,7 @@
           <t>(16,17)</t>
         </is>
       </c>
+      <c r="J665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -22314,6 +23199,7 @@
           <t>(16,18)</t>
         </is>
       </c>
+      <c r="J666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -22344,6 +23230,7 @@
           <t>(16,19)</t>
         </is>
       </c>
+      <c r="J667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -22374,6 +23261,7 @@
           <t>(16,20)</t>
         </is>
       </c>
+      <c r="J668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -22404,6 +23292,7 @@
           <t>(16,21)</t>
         </is>
       </c>
+      <c r="J669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -22434,6 +23323,7 @@
           <t>(16,22)</t>
         </is>
       </c>
+      <c r="J670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -22464,6 +23354,7 @@
           <t>(16,23)</t>
         </is>
       </c>
+      <c r="J671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -22494,6 +23385,7 @@
           <t>(16,24)</t>
         </is>
       </c>
+      <c r="J672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -22524,6 +23416,7 @@
           <t>(16,25)</t>
         </is>
       </c>
+      <c r="J673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -22554,6 +23447,7 @@
           <t>(16,26)</t>
         </is>
       </c>
+      <c r="J674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -22584,6 +23478,7 @@
           <t>(16,27)</t>
         </is>
       </c>
+      <c r="J675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -22614,6 +23509,7 @@
           <t>(17,18)</t>
         </is>
       </c>
+      <c r="J676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -22644,6 +23540,7 @@
           <t>(17,19)</t>
         </is>
       </c>
+      <c r="J677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -22674,6 +23571,7 @@
           <t>(17,20)</t>
         </is>
       </c>
+      <c r="J678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -22704,6 +23602,7 @@
           <t>(17,21)</t>
         </is>
       </c>
+      <c r="J679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -22734,6 +23633,7 @@
           <t>(17,22)</t>
         </is>
       </c>
+      <c r="J680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -22764,6 +23664,7 @@
           <t>(17,23)</t>
         </is>
       </c>
+      <c r="J681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -22794,6 +23695,7 @@
           <t>(17,24)</t>
         </is>
       </c>
+      <c r="J682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -22824,6 +23726,7 @@
           <t>(17,25)</t>
         </is>
       </c>
+      <c r="J683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -22854,6 +23757,7 @@
           <t>(17,26)</t>
         </is>
       </c>
+      <c r="J684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -22884,6 +23788,7 @@
           <t>(17,27)</t>
         </is>
       </c>
+      <c r="J685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -22914,6 +23819,7 @@
           <t>(18,19)</t>
         </is>
       </c>
+      <c r="J686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -22944,6 +23850,7 @@
           <t>(18,20)</t>
         </is>
       </c>
+      <c r="J687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -22974,6 +23881,7 @@
           <t>(18,21)</t>
         </is>
       </c>
+      <c r="J688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -23004,6 +23912,7 @@
           <t>(18,22)</t>
         </is>
       </c>
+      <c r="J689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -23034,6 +23943,7 @@
           <t>(18,23)</t>
         </is>
       </c>
+      <c r="J690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -23064,6 +23974,7 @@
           <t>(18,24)</t>
         </is>
       </c>
+      <c r="J691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -23094,6 +24005,7 @@
           <t>(18,25)</t>
         </is>
       </c>
+      <c r="J692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -23124,6 +24036,7 @@
           <t>(18,26)</t>
         </is>
       </c>
+      <c r="J693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -23154,6 +24067,7 @@
           <t>(18,27)</t>
         </is>
       </c>
+      <c r="J694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -23184,6 +24098,7 @@
           <t>(19,20)</t>
         </is>
       </c>
+      <c r="J695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -23214,6 +24129,7 @@
           <t>(19,21)</t>
         </is>
       </c>
+      <c r="J696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -23244,6 +24160,7 @@
           <t>(19,22)</t>
         </is>
       </c>
+      <c r="J697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -23274,6 +24191,7 @@
           <t>(19,23)</t>
         </is>
       </c>
+      <c r="J698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -23304,6 +24222,7 @@
           <t>(19,24)</t>
         </is>
       </c>
+      <c r="J699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -23334,6 +24253,7 @@
           <t>(19,25)</t>
         </is>
       </c>
+      <c r="J700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -23364,6 +24284,7 @@
           <t>(19,26)</t>
         </is>
       </c>
+      <c r="J701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -23394,6 +24315,7 @@
           <t>(19,27)</t>
         </is>
       </c>
+      <c r="J702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -23424,6 +24346,7 @@
           <t>(20,21)</t>
         </is>
       </c>
+      <c r="J703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -23454,6 +24377,7 @@
           <t>(20,22)</t>
         </is>
       </c>
+      <c r="J704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -23484,6 +24408,7 @@
           <t>(20,23)</t>
         </is>
       </c>
+      <c r="J705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -23514,6 +24439,7 @@
           <t>(20,24)</t>
         </is>
       </c>
+      <c r="J706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -23544,6 +24470,7 @@
           <t>(20,25)</t>
         </is>
       </c>
+      <c r="J707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -23574,6 +24501,7 @@
           <t>(20,26)</t>
         </is>
       </c>
+      <c r="J708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -23604,6 +24532,7 @@
           <t>(20,27)</t>
         </is>
       </c>
+      <c r="J709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -23634,6 +24563,7 @@
           <t>(21,22)</t>
         </is>
       </c>
+      <c r="J710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -23664,6 +24594,7 @@
           <t>(21,23)</t>
         </is>
       </c>
+      <c r="J711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -23694,6 +24625,7 @@
           <t>(21,24)</t>
         </is>
       </c>
+      <c r="J712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -23724,6 +24656,7 @@
           <t>(21,25)</t>
         </is>
       </c>
+      <c r="J713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -23754,6 +24687,7 @@
           <t>(21,26)</t>
         </is>
       </c>
+      <c r="J714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -23784,6 +24718,7 @@
           <t>(21,27)</t>
         </is>
       </c>
+      <c r="J715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -23814,6 +24749,7 @@
           <t>(22,23)</t>
         </is>
       </c>
+      <c r="J716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -23844,6 +24780,7 @@
           <t>(22,24)</t>
         </is>
       </c>
+      <c r="J717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -23874,6 +24811,7 @@
           <t>(22,25)</t>
         </is>
       </c>
+      <c r="J718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -23904,6 +24842,7 @@
           <t>(22,26)</t>
         </is>
       </c>
+      <c r="J719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -23934,6 +24873,7 @@
           <t>(22,27)</t>
         </is>
       </c>
+      <c r="J720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -23964,6 +24904,7 @@
           <t>(23,24)</t>
         </is>
       </c>
+      <c r="J721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -23994,6 +24935,7 @@
           <t>(23,25)</t>
         </is>
       </c>
+      <c r="J722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -24024,6 +24966,7 @@
           <t>(23,26)</t>
         </is>
       </c>
+      <c r="J723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -24054,6 +24997,7 @@
           <t>(23,27)</t>
         </is>
       </c>
+      <c r="J724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -24084,6 +25028,7 @@
           <t>(24,25)</t>
         </is>
       </c>
+      <c r="J725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -24114,6 +25059,7 @@
           <t>(24,26)</t>
         </is>
       </c>
+      <c r="J726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -24144,6 +25090,7 @@
           <t>(24,27)</t>
         </is>
       </c>
+      <c r="J727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -24174,6 +25121,7 @@
           <t>(25,26)</t>
         </is>
       </c>
+      <c r="J728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -24204,6 +25152,7 @@
           <t>(25,27)</t>
         </is>
       </c>
+      <c r="J729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -24234,6 +25183,7 @@
           <t>(26,27)</t>
         </is>
       </c>
+      <c r="J730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -24260,6 +25210,7 @@
         </is>
       </c>
       <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -24286,6 +25237,7 @@
         </is>
       </c>
       <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J732"/>
+  <dimension ref="A1:J734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,8 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -524,8 +523,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -565,8 +563,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -606,8 +603,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -647,8 +643,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -688,8 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -729,8 +723,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -770,8 +763,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -811,8 +803,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -852,8 +843,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -893,8 +883,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -934,8 +923,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -975,8 +963,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1016,8 +1003,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1057,8 +1043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1098,8 +1083,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1139,8 +1123,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1180,8 +1163,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1221,8 +1203,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1262,8 +1243,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1303,8 +1283,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1344,8 +1323,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1385,8 +1363,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1426,8 +1403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1467,8 +1443,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1508,8 +1483,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1549,8 +1523,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>within epitope
-within mice</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1590,8 +1563,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1633,8 +1605,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1676,8 +1647,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1719,8 +1689,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1762,8 +1731,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1805,8 +1773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1848,8 +1815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1891,8 +1857,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1934,8 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1977,8 +1941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2020,8 +1983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2063,8 +2025,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2106,8 +2067,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2149,8 +2109,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2192,8 +2151,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2235,8 +2193,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2278,8 +2235,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2321,8 +2277,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2364,8 +2319,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2407,8 +2361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2450,8 +2403,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2493,8 +2445,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2536,8 +2487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2579,8 +2529,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2622,8 +2571,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2665,8 +2613,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2708,8 +2655,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2751,8 +2697,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2794,8 +2739,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2837,8 +2781,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2880,8 +2823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2923,8 +2865,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2966,8 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -3009,8 +2949,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -3052,8 +2991,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3095,8 +3033,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3138,8 +3075,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3181,8 +3117,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3224,8 +3159,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3267,8 +3201,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3310,8 +3243,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3353,8 +3285,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3396,8 +3327,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3439,8 +3369,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3482,8 +3411,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3525,8 +3453,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3568,8 +3495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3611,8 +3537,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3654,8 +3579,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3697,8 +3621,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3740,8 +3663,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3783,8 +3705,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3826,8 +3747,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3869,8 +3789,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>within strain &amp; epitope
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3912,8 +3831,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3947,8 +3865,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3982,8 +3899,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -4017,8 +3933,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -4052,8 +3967,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4087,8 +4001,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4122,8 +4035,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4157,8 +4069,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4192,8 +4103,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4227,8 +4137,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4262,8 +4171,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4297,8 +4205,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4332,8 +4239,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4367,8 +4273,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4402,8 +4307,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4437,8 +4341,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4472,8 +4375,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4507,8 +4409,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4542,8 +4443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4577,8 +4477,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4612,8 +4511,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4647,8 +4545,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4682,8 +4579,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4717,8 +4613,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4752,8 +4647,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4787,8 +4681,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4822,8 +4715,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4857,8 +4749,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4892,8 +4783,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4927,8 +4817,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4962,8 +4851,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4997,8 +4885,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -5032,8 +4919,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -5067,8 +4953,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -5102,8 +4987,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -5137,8 +5021,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5172,8 +5055,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5207,8 +5089,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5242,8 +5123,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5277,8 +5157,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5312,8 +5191,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5347,8 +5225,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5382,8 +5259,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5417,8 +5293,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5452,8 +5327,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5487,8 +5361,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5522,8 +5395,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5557,8 +5429,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5592,8 +5463,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5627,8 +5497,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5662,8 +5531,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5697,8 +5565,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5732,8 +5599,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5767,8 +5633,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5802,8 +5667,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5837,8 +5701,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5872,8 +5735,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5907,8 +5769,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5942,8 +5803,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5977,8 +5837,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -6012,8 +5871,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -6047,8 +5905,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -6082,8 +5939,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -6117,8 +5973,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -6152,8 +6007,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -6187,8 +6041,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6222,8 +6075,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6257,8 +6109,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6292,8 +6143,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6327,8 +6177,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6362,8 +6211,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6397,8 +6245,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6432,8 +6279,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6467,8 +6313,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6502,8 +6347,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6537,8 +6381,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6572,8 +6415,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6607,8 +6449,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6642,8 +6483,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6677,8 +6517,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6712,8 +6551,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6747,8 +6585,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6782,8 +6619,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6817,8 +6653,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6852,8 +6687,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6887,8 +6721,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6922,8 +6755,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6957,8 +6789,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6992,8 +6823,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -7027,8 +6857,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -7062,8 +6891,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -7097,8 +6925,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -7132,8 +6959,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -7167,8 +6993,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7202,8 +7027,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -7237,8 +7061,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -7272,8 +7095,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -7307,8 +7129,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -7342,8 +7163,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7377,8 +7197,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7412,8 +7231,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7447,8 +7265,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7482,8 +7299,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -7517,8 +7333,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -7552,8 +7367,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -7587,8 +7401,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -7622,8 +7435,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7657,8 +7469,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -7692,8 +7503,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7727,8 +7537,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7762,8 +7571,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -7797,8 +7605,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -7832,8 +7639,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -7867,8 +7673,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -7902,8 +7707,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -7937,8 +7741,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -7972,8 +7775,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -8007,8 +7809,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -8042,8 +7843,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -8077,8 +7877,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -8112,8 +7911,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -8147,8 +7945,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -8182,8 +7979,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -8217,8 +8013,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8252,8 +8047,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -8287,8 +8081,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -8322,8 +8115,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -8357,8 +8149,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -8392,8 +8183,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -8427,8 +8217,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -8462,8 +8251,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -8497,8 +8285,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -8532,8 +8319,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -8567,8 +8353,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -8602,8 +8387,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -8637,8 +8421,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -8672,8 +8455,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -8707,8 +8489,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -8742,8 +8523,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -8777,8 +8557,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -8812,8 +8591,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -8847,8 +8625,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -8882,8 +8659,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -8917,8 +8693,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -8952,8 +8727,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -8987,8 +8761,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -9022,8 +8795,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -9057,8 +8829,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -9092,8 +8863,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -9127,8 +8897,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -9162,8 +8931,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -9197,8 +8965,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -9232,8 +8999,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -9267,8 +9033,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -9302,8 +9067,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -9337,8 +9101,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -9372,8 +9135,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -9407,8 +9169,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -9442,8 +9203,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -9477,8 +9237,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -9512,8 +9271,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -9547,8 +9305,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -9582,8 +9339,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -9617,8 +9373,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -9652,8 +9407,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -9687,8 +9441,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -9722,8 +9475,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9757,8 +9509,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9792,8 +9543,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -9827,8 +9577,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -9862,8 +9611,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -9897,8 +9645,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -9932,8 +9679,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -9967,8 +9713,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -10002,8 +9747,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -10037,8 +9781,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -10072,8 +9815,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -10107,8 +9849,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -10142,8 +9883,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -10177,8 +9917,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -10212,8 +9951,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -10247,8 +9985,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -10282,8 +10019,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -10317,8 +10053,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -10352,8 +10087,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -10387,8 +10121,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -10422,8 +10155,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -10457,8 +10189,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -10492,8 +10223,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -10527,8 +10257,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -10562,8 +10291,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -10597,8 +10325,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -10632,8 +10359,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -10667,8 +10393,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -10702,8 +10427,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -10737,8 +10461,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -10772,8 +10495,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -10807,8 +10529,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -10842,8 +10563,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -10877,8 +10597,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -10912,8 +10631,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -10947,8 +10665,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -10982,8 +10699,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -11017,8 +10733,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -11052,8 +10767,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -11087,8 +10801,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -11122,8 +10835,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -11157,8 +10869,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -11192,8 +10903,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -11227,8 +10937,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -11262,8 +10971,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -11297,8 +11005,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -11332,8 +11039,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -11367,8 +11073,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -11402,8 +11107,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -11437,8 +11141,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -11472,8 +11175,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -11507,8 +11209,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -11542,8 +11243,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -11577,8 +11277,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -11612,8 +11311,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -11647,8 +11345,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -11682,8 +11379,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -11717,8 +11413,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -11752,8 +11447,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -11787,8 +11481,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -11822,8 +11515,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -11857,8 +11549,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -11892,8 +11583,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -11927,8 +11617,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -11962,8 +11651,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -11997,8 +11685,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -12032,8 +11719,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -12067,8 +11753,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -12102,8 +11787,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -12137,8 +11821,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -12172,8 +11855,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -12207,8 +11889,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -12242,8 +11923,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -12277,8 +11957,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -12312,8 +11991,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -12347,8 +12025,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -12382,8 +12059,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -12417,8 +12093,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -12452,8 +12127,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -12487,8 +12161,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -12522,8 +12195,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -12557,8 +12229,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -12592,8 +12263,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -12627,8 +12297,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -12662,8 +12331,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -12697,8 +12365,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -12732,8 +12399,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -12767,8 +12433,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -12802,8 +12467,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -12837,8 +12501,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -12872,8 +12535,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -12907,8 +12569,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -12942,8 +12603,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -12977,8 +12637,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -13012,8 +12671,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -13047,8 +12705,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -13082,8 +12739,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -13117,8 +12773,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -13152,8 +12807,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -13187,8 +12841,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -13222,8 +12875,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -13257,8 +12909,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -13292,8 +12943,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -13327,8 +12977,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -13362,8 +13011,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -13397,8 +13045,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -13432,8 +13079,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -13467,8 +13113,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -13502,8 +13147,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -13537,8 +13181,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -13572,8 +13215,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -13607,8 +13249,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -13642,8 +13283,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -13677,8 +13317,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -13712,8 +13351,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -13747,8 +13385,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -13782,8 +13419,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -13817,8 +13453,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -13852,8 +13487,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -13887,8 +13521,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -13922,8 +13555,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -13957,8 +13589,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -13992,8 +13623,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -14027,8 +13657,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -14062,8 +13691,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -14097,8 +13725,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -14132,8 +13759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -14167,8 +13793,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -14202,8 +13827,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -14237,8 +13861,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -14272,8 +13895,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -14307,8 +13929,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -14338,8 +13959,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -14369,8 +13989,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -14400,8 +14019,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -14431,8 +14049,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -14462,8 +14079,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -14493,8 +14109,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -14524,8 +14139,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -14555,8 +14169,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -14586,8 +14199,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -14617,8 +14229,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -14648,8 +14259,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -14679,8 +14289,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -14710,8 +14319,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -14741,8 +14349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -14772,8 +14379,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -14803,8 +14409,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -14834,8 +14439,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -14865,8 +14469,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -14896,8 +14499,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -14927,8 +14529,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -14958,8 +14559,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -14989,8 +14589,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -15020,8 +14619,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -15051,8 +14649,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -15082,8 +14679,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -15113,8 +14709,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -15144,8 +14739,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -15175,8 +14769,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -15206,8 +14799,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -15237,8 +14829,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -15268,8 +14859,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -15299,8 +14889,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -15330,8 +14919,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -15361,8 +14949,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -15392,8 +14979,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -15423,8 +15009,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -15454,8 +15039,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -15485,8 +15069,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -15516,8 +15099,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -15547,8 +15129,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -15578,8 +15159,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -15609,8 +15189,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -15640,8 +15219,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -15671,8 +15249,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -15702,8 +15279,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -15733,8 +15309,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15764,8 +15339,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -15795,8 +15369,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -15826,8 +15399,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15857,8 +15429,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -15888,8 +15459,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -15919,8 +15489,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -15950,8 +15519,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -15981,8 +15549,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -16012,8 +15579,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -16043,8 +15609,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -16074,8 +15639,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -16105,8 +15669,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -16136,8 +15699,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -16167,8 +15729,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -16198,8 +15759,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -16229,8 +15789,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -16260,8 +15819,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -16291,8 +15849,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -16322,8 +15879,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -16353,8 +15909,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -16384,8 +15939,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -16415,8 +15969,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -16446,8 +15999,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -16477,8 +16029,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -16508,8 +16059,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -16539,8 +16089,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -16570,8 +16119,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -16601,8 +16149,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -16632,8 +16179,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -16663,8 +16209,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16694,8 +16239,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -16725,8 +16269,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -16756,8 +16299,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -16787,8 +16329,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -16818,8 +16359,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -16849,8 +16389,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -16880,8 +16419,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -16911,8 +16449,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -16942,8 +16479,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -16973,8 +16509,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -17004,8 +16539,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -17035,8 +16569,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -17066,8 +16599,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -17097,8 +16629,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -17128,8 +16659,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -17159,8 +16689,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -17190,8 +16719,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -17221,8 +16749,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -17252,8 +16779,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -17283,8 +16809,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -17314,8 +16839,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -17345,8 +16869,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -17376,8 +16899,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -17407,8 +16929,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -17438,8 +16959,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -17469,8 +16989,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -17500,8 +17019,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -17531,8 +17049,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -17562,8 +17079,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -17593,8 +17109,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -17624,8 +17139,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -17655,8 +17169,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -17686,8 +17199,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -17717,8 +17229,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -17748,8 +17259,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -17779,8 +17289,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -17810,8 +17319,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -17841,8 +17349,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -17872,8 +17379,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -17903,8 +17409,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -17934,8 +17439,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -17965,8 +17469,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -17996,8 +17499,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -18027,8 +17529,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -18058,8 +17559,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -18089,8 +17589,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -18120,8 +17619,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -18151,8 +17649,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -18182,8 +17679,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -18213,8 +17709,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
@@ -18244,8 +17739,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -18275,8 +17769,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
@@ -18306,8 +17799,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
@@ -18337,8 +17829,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -18368,8 +17859,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
@@ -18399,8 +17889,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
@@ -18430,8 +17919,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -18461,8 +17949,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
@@ -18492,8 +17979,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
@@ -18523,8 +18009,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -18554,8 +18039,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
@@ -18585,8 +18069,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
@@ -18616,8 +18099,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -18647,8 +18129,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
@@ -18678,8 +18159,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
@@ -18709,8 +18189,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -18740,8 +18219,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -18771,8 +18249,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -18802,8 +18279,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -18833,8 +18309,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -18864,8 +18339,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -18895,8 +18369,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -18926,8 +18399,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -18957,8 +18429,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
@@ -18988,8 +18459,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -19019,8 +18489,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -19050,8 +18519,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B533" t="inlineStr"/>
@@ -19081,8 +18549,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -19112,8 +18579,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B535" t="inlineStr"/>
@@ -19143,8 +18609,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B536" t="inlineStr"/>
@@ -19174,8 +18639,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -19205,8 +18669,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -19236,8 +18699,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
@@ -19267,8 +18729,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -19298,8 +18759,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
@@ -19329,8 +18789,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
@@ -19360,8 +18819,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -19391,8 +18849,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
@@ -19422,8 +18879,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B545" t="inlineStr"/>
@@ -19453,8 +18909,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -19484,8 +18939,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B547" t="inlineStr"/>
@@ -19515,8 +18969,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
@@ -19546,8 +18999,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -19577,8 +19029,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B550" t="inlineStr"/>
@@ -19608,8 +19059,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B551" t="inlineStr"/>
@@ -19639,8 +19089,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -19670,8 +19119,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B553" t="inlineStr"/>
@@ -19701,8 +19149,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B554" t="inlineStr"/>
@@ -19732,8 +19179,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -19763,8 +19209,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
@@ -19794,8 +19239,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
@@ -19825,8 +19269,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -19856,8 +19299,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
@@ -19887,8 +19329,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
@@ -19918,8 +19359,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -19949,8 +19389,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
@@ -19980,8 +19419,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
@@ -20011,8 +19449,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -20042,8 +19479,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
@@ -20073,8 +19509,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
@@ -20104,8 +19539,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
@@ -20135,8 +19569,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
@@ -20166,8 +19599,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
@@ -20197,8 +19629,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
@@ -20228,8 +19659,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
@@ -20259,8 +19689,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
@@ -20290,8 +19719,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
@@ -20321,8 +19749,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B574" t="inlineStr"/>
@@ -20352,8 +19779,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
@@ -20383,8 +19809,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
@@ -20414,8 +19839,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
@@ -20445,8 +19869,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B578" t="inlineStr"/>
@@ -20476,8 +19899,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -20507,8 +19929,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
@@ -20538,8 +19959,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
@@ -20569,8 +19989,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
@@ -20600,8 +20019,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
@@ -20631,8 +20049,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
@@ -20662,8 +20079,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -20693,8 +20109,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
@@ -20724,8 +20139,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
@@ -20755,8 +20169,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -20786,8 +20199,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B589" t="inlineStr"/>
@@ -20817,8 +20229,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -20848,8 +20259,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -20879,8 +20289,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -20910,8 +20319,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
@@ -20941,8 +20349,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -20972,8 +20379,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
@@ -21003,8 +20409,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B596" t="inlineStr"/>
@@ -21034,8 +20439,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -21065,8 +20469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -21096,8 +20499,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -21127,8 +20529,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -21158,8 +20559,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -21189,8 +20589,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -21220,8 +20619,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -21251,8 +20649,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -21282,8 +20679,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -21313,8 +20709,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -21344,8 +20739,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -21375,8 +20769,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -21406,8 +20799,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -21437,8 +20829,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
@@ -21468,8 +20859,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
@@ -21499,8 +20889,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -21530,8 +20919,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
@@ -21561,8 +20949,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
@@ -21592,8 +20979,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -21623,8 +21009,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
@@ -21654,8 +21039,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
@@ -21685,8 +21069,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -21716,8 +21099,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
@@ -21747,8 +21129,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
@@ -21778,8 +21159,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -21809,8 +21189,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
@@ -21840,8 +21219,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
@@ -21871,8 +21249,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -21902,8 +21279,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
@@ -21933,8 +21309,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B626" t="inlineStr"/>
@@ -21964,8 +21339,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -21995,8 +21369,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
@@ -22026,8 +21399,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
@@ -22057,8 +21429,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -22088,8 +21459,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
@@ -22119,8 +21489,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
@@ -22150,8 +21519,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -22181,8 +21549,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
@@ -22212,8 +21579,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
@@ -22243,8 +21609,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
@@ -22274,8 +21639,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B637" t="inlineStr"/>
@@ -22305,8 +21669,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B638" t="inlineStr"/>
@@ -22336,8 +21699,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B639" t="inlineStr"/>
@@ -22367,8 +21729,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B640" t="inlineStr"/>
@@ -22398,8 +21759,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
@@ -22429,8 +21789,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
@@ -22460,8 +21819,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
@@ -22491,8 +21849,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
@@ -22522,8 +21879,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B645" t="inlineStr"/>
@@ -22553,8 +21909,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B646" t="inlineStr"/>
@@ -22584,8 +21939,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B647" t="inlineStr"/>
@@ -22615,8 +21969,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -22646,8 +21999,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B649" t="inlineStr"/>
@@ -22677,8 +22029,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B650" t="inlineStr"/>
@@ -22708,8 +22059,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -22739,8 +22089,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B652" t="inlineStr"/>
@@ -22770,8 +22119,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B653" t="inlineStr"/>
@@ -22801,8 +22149,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -22832,8 +22179,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B655" t="inlineStr"/>
@@ -22863,8 +22209,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -22894,8 +22239,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -22925,8 +22269,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B658" t="inlineStr"/>
@@ -22956,8 +22299,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B659" t="inlineStr"/>
@@ -22987,8 +22329,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -23018,8 +22359,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -23049,8 +22389,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B662" t="inlineStr"/>
@@ -23080,8 +22419,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -23111,8 +22449,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B664" t="inlineStr"/>
@@ -23142,8 +22479,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B665" t="inlineStr"/>
@@ -23173,8 +22509,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B666" t="inlineStr"/>
@@ -23204,8 +22539,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B667" t="inlineStr"/>
@@ -23235,8 +22569,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B668" t="inlineStr"/>
@@ -23266,8 +22599,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B669" t="inlineStr"/>
@@ -23297,8 +22629,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B670" t="inlineStr"/>
@@ -23328,8 +22659,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B671" t="inlineStr"/>
@@ -23359,8 +22689,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B672" t="inlineStr"/>
@@ -23390,8 +22719,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B673" t="inlineStr"/>
@@ -23421,8 +22749,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B674" t="inlineStr"/>
@@ -23452,8 +22779,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B675" t="inlineStr"/>
@@ -23483,8 +22809,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B676" t="inlineStr"/>
@@ -23514,8 +22839,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B677" t="inlineStr"/>
@@ -23545,8 +22869,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
@@ -23576,8 +22899,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
@@ -23607,8 +22929,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B680" t="inlineStr"/>
@@ -23638,8 +22959,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
@@ -23669,8 +22989,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B682" t="inlineStr"/>
@@ -23700,8 +23019,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B683" t="inlineStr"/>
@@ -23731,8 +23049,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
@@ -23762,8 +23079,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B685" t="inlineStr"/>
@@ -23793,8 +23109,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B686" t="inlineStr"/>
@@ -23824,8 +23139,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
@@ -23855,8 +23169,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B688" t="inlineStr"/>
@@ -23886,8 +23199,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B689" t="inlineStr"/>
@@ -23917,8 +23229,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -23948,8 +23259,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B691" t="inlineStr"/>
@@ -23979,8 +23289,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B692" t="inlineStr"/>
@@ -24010,8 +23319,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -24041,8 +23349,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B694" t="inlineStr"/>
@@ -24072,8 +23379,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B695" t="inlineStr"/>
@@ -24103,8 +23409,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B696" t="inlineStr"/>
@@ -24134,8 +23439,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B697" t="inlineStr"/>
@@ -24165,8 +23469,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B698" t="inlineStr"/>
@@ -24196,8 +23499,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B699" t="inlineStr"/>
@@ -24227,8 +23529,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B700" t="inlineStr"/>
@@ -24258,8 +23559,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B701" t="inlineStr"/>
@@ -24289,8 +23589,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -24320,8 +23619,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B703" t="inlineStr"/>
@@ -24351,8 +23649,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B704" t="inlineStr"/>
@@ -24382,8 +23679,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B705" t="inlineStr"/>
@@ -24413,8 +23709,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B706" t="inlineStr"/>
@@ -24444,8 +23739,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B707" t="inlineStr"/>
@@ -24475,8 +23769,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B708" t="inlineStr"/>
@@ -24506,8 +23799,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B709" t="inlineStr"/>
@@ -24537,8 +23829,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B710" t="inlineStr"/>
@@ -24568,8 +23859,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B711" t="inlineStr"/>
@@ -24599,8 +23889,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B712" t="inlineStr"/>
@@ -24630,8 +23919,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B713" t="inlineStr"/>
@@ -24661,8 +23949,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B714" t="inlineStr"/>
@@ -24692,8 +23979,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B715" t="inlineStr"/>
@@ -24723,8 +24009,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B716" t="inlineStr"/>
@@ -24754,8 +24039,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
@@ -24785,8 +24069,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B718" t="inlineStr"/>
@@ -24816,8 +24099,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B719" t="inlineStr"/>
@@ -24847,8 +24129,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
@@ -24878,8 +24159,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B721" t="inlineStr"/>
@@ -24909,8 +24189,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B722" t="inlineStr"/>
@@ -24940,8 +24219,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
@@ -24971,8 +24249,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B724" t="inlineStr"/>
@@ -25002,8 +24279,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B725" t="inlineStr"/>
@@ -25033,8 +24309,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B726" t="inlineStr"/>
@@ -25064,8 +24339,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B727" t="inlineStr"/>
@@ -25095,8 +24369,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B728" t="inlineStr"/>
@@ -25126,8 +24399,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B729" t="inlineStr"/>
@@ -25157,8 +24429,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>across strain
-across epitope</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="B730" t="inlineStr"/>
@@ -25188,8 +24459,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Pre-Immune
-Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B731" t="inlineStr"/>
@@ -25206,7 +24476,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Pre-Immune</t>
+          <t>B10BR SLO</t>
         </is>
       </c>
       <c r="I731" t="inlineStr"/>
@@ -25215,8 +24485,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Pre-Immune
-Repertoires</t>
+          <t>Pre-Immune Repertoire</t>
         </is>
       </c>
       <c r="B732" t="inlineStr"/>
@@ -25233,11 +24502,63 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Pre-Immune</t>
+          <t>BALBc SLO</t>
         </is>
       </c>
       <c r="I732" t="inlineStr"/>
       <c r="J732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr"/>
+      <c r="C733" t="inlineStr"/>
+      <c r="D733" t="inlineStr"/>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="n">
+        <v>1.83563638392849e-07</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>B10BR Kb × B10BR Kd</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>B10BR Kb × B10BR Kd</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Pre-Immune Repertoire</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr"/>
+      <c r="C734" t="inlineStr"/>
+      <c r="D734" t="inlineStr"/>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="n">
+        <v>7.793067754860183e-07</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>B10BR SLO × BALBc SLO</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>B10BR SLO × BALBc SLO</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
@@ -1563,7 +1563,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1857,7 +1857,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1899,7 +1899,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -2277,7 +2277,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2319,7 +2319,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2403,7 +2403,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2571,7 +2571,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2613,7 +2613,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2655,7 +2655,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2823,7 +2823,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2907,7 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2991,7 +2991,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -3201,7 +3201,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -3285,7 +3285,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -3495,7 +3495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3579,7 +3579,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3621,7 +3621,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3705,7 +3705,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3747,7 +3747,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Same strain, same epitope</t>
+          <t>Same strain, same peptide</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3831,7 +3831,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3899,7 +3899,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -4035,7 +4035,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -4069,7 +4069,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -4137,7 +4137,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -4239,7 +4239,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -4341,7 +4341,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -4375,7 +4375,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -4409,7 +4409,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -4477,7 +4477,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -4579,7 +4579,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -4613,7 +4613,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -4647,7 +4647,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4681,7 +4681,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4715,7 +4715,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4749,7 +4749,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4783,7 +4783,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4817,7 +4817,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4851,7 +4851,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -4885,7 +4885,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -4919,7 +4919,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -4953,7 +4953,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4987,7 +4987,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -5055,7 +5055,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -5089,7 +5089,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -5123,7 +5123,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -5157,7 +5157,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -5191,7 +5191,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -5225,7 +5225,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -5259,7 +5259,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -5293,7 +5293,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -5361,7 +5361,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -5395,7 +5395,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -5429,7 +5429,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -5463,7 +5463,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5497,7 +5497,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -5565,7 +5565,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5599,7 +5599,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5667,7 +5667,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5701,7 +5701,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5735,7 +5735,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5803,7 +5803,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
@@ -5871,7 +5871,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5905,7 +5905,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5939,7 +5939,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5973,7 +5973,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -6007,7 +6007,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -6041,7 +6041,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -6075,7 +6075,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -6109,7 +6109,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -6143,7 +6143,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -6177,7 +6177,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -6245,7 +6245,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -6313,7 +6313,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -6347,7 +6347,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -6415,7 +6415,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -6449,7 +6449,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -6483,7 +6483,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -6517,7 +6517,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
@@ -6585,7 +6585,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -6653,7 +6653,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -6721,7 +6721,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -6755,7 +6755,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
@@ -6789,7 +6789,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -6823,7 +6823,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -6857,7 +6857,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
@@ -6891,7 +6891,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -6925,7 +6925,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -6959,7 +6959,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -7027,7 +7027,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -7061,7 +7061,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
@@ -7095,7 +7095,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -7129,7 +7129,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -7163,7 +7163,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7197,7 +7197,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7265,7 +7265,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -7299,7 +7299,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -7333,7 +7333,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -7367,7 +7367,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -7435,7 +7435,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -7469,7 +7469,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Same epitope, different strain</t>
+          <t>Same peptide, different strain</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
@@ -7503,7 +7503,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -7537,7 +7537,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -7571,7 +7571,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
@@ -7605,7 +7605,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -7639,7 +7639,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
@@ -7707,7 +7707,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -7741,7 +7741,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -7809,7 +7809,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -7843,7 +7843,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -7877,7 +7877,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
@@ -7911,7 +7911,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -7979,7 +7979,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -8013,7 +8013,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -8081,7 +8081,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -8149,7 +8149,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -8183,7 +8183,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -8217,7 +8217,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -8285,7 +8285,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -8353,7 +8353,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -8421,7 +8421,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -8455,7 +8455,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -8489,7 +8489,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
@@ -8523,7 +8523,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -8557,7 +8557,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -8591,7 +8591,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -8659,7 +8659,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -8693,7 +8693,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -8727,7 +8727,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -8761,7 +8761,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
@@ -8829,7 +8829,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -8863,7 +8863,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -8897,7 +8897,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -8931,7 +8931,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -8965,7 +8965,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -9033,7 +9033,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -9067,7 +9067,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -9101,7 +9101,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -9135,7 +9135,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -9169,7 +9169,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -9237,7 +9237,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -9271,7 +9271,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -9305,7 +9305,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -9339,7 +9339,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -9373,7 +9373,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -9407,7 +9407,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
@@ -9441,7 +9441,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -9475,7 +9475,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -9509,7 +9509,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -9577,7 +9577,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -9611,7 +9611,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -9645,7 +9645,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -9679,7 +9679,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -9713,7 +9713,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -9747,7 +9747,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -9781,7 +9781,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -9815,7 +9815,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
@@ -9849,7 +9849,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -9883,7 +9883,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -9917,7 +9917,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
@@ -9951,7 +9951,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -9985,7 +9985,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -10019,7 +10019,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -10053,7 +10053,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -10087,7 +10087,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -10121,7 +10121,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -10155,7 +10155,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -10189,7 +10189,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -10223,7 +10223,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -10257,7 +10257,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -10291,7 +10291,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -10325,7 +10325,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -10359,7 +10359,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -10393,7 +10393,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -10427,7 +10427,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -10461,7 +10461,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -10495,7 +10495,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -10529,7 +10529,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -10563,7 +10563,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -10597,7 +10597,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -10631,7 +10631,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -10699,7 +10699,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -10733,7 +10733,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -10767,7 +10767,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -10801,7 +10801,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -10835,7 +10835,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
@@ -10869,7 +10869,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -10903,7 +10903,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -10937,7 +10937,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -10971,7 +10971,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -11005,7 +11005,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -11039,7 +11039,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -11073,7 +11073,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -11107,7 +11107,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -11175,7 +11175,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -11209,7 +11209,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -11243,7 +11243,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -11277,7 +11277,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -11345,7 +11345,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -11379,7 +11379,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -11413,7 +11413,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -11447,7 +11447,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -11481,7 +11481,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -11549,7 +11549,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -11583,7 +11583,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -11651,7 +11651,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
@@ -11685,7 +11685,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -11719,7 +11719,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -11821,7 +11821,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -11855,7 +11855,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -11889,7 +11889,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -11923,7 +11923,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -11957,7 +11957,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -11991,7 +11991,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -12025,7 +12025,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -12059,7 +12059,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -12093,7 +12093,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -12127,7 +12127,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -12161,7 +12161,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -12195,7 +12195,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -12229,7 +12229,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -12263,7 +12263,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -12297,7 +12297,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -12331,7 +12331,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -12365,7 +12365,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -12399,7 +12399,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -12433,7 +12433,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -12467,7 +12467,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
@@ -12501,7 +12501,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -12535,7 +12535,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -12569,7 +12569,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -12603,7 +12603,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -12637,7 +12637,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -12671,7 +12671,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -12705,7 +12705,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -12739,7 +12739,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -12773,7 +12773,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -12807,7 +12807,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -12841,7 +12841,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -12875,7 +12875,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -12943,7 +12943,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -12977,7 +12977,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -13011,7 +13011,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -13045,7 +13045,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -13079,7 +13079,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -13113,7 +13113,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -13147,7 +13147,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -13181,7 +13181,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -13249,7 +13249,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -13283,7 +13283,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -13317,7 +13317,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -13351,7 +13351,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -13385,7 +13385,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -13419,7 +13419,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -13453,7 +13453,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -13487,7 +13487,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -13555,7 +13555,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -13589,7 +13589,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -13623,7 +13623,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -13657,7 +13657,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -13725,7 +13725,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -13759,7 +13759,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -13793,7 +13793,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -13827,7 +13827,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -13861,7 +13861,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -13895,7 +13895,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Same strain, different epitope</t>
+          <t>Same strain, different peptide</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -13929,7 +13929,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -13959,7 +13959,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -13989,7 +13989,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -14019,7 +14019,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -14049,7 +14049,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -14079,7 +14079,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -14109,7 +14109,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -14139,7 +14139,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -14169,7 +14169,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B388" t="inlineStr"/>
@@ -14199,7 +14199,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -14259,7 +14259,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B391" t="inlineStr"/>
@@ -14289,7 +14289,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -14319,7 +14319,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -14349,7 +14349,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B394" t="inlineStr"/>
@@ -14379,7 +14379,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -14409,7 +14409,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B397" t="inlineStr"/>
@@ -14469,7 +14469,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -14499,7 +14499,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -14529,7 +14529,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B400" t="inlineStr"/>
@@ -14559,7 +14559,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -14589,7 +14589,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -14619,7 +14619,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B403" t="inlineStr"/>
@@ -14649,7 +14649,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -14709,7 +14709,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B406" t="inlineStr"/>
@@ -14739,7 +14739,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -14769,7 +14769,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -14799,7 +14799,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B409" t="inlineStr"/>
@@ -14829,7 +14829,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -14859,7 +14859,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
@@ -14919,7 +14919,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -14949,7 +14949,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -14979,7 +14979,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -15009,7 +15009,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -15039,7 +15039,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -15069,7 +15069,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B418" t="inlineStr"/>
@@ -15099,7 +15099,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -15129,7 +15129,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -15159,7 +15159,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B421" t="inlineStr"/>
@@ -15189,7 +15189,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -15219,7 +15219,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -15249,7 +15249,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B424" t="inlineStr"/>
@@ -15279,7 +15279,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -15309,7 +15309,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -15339,7 +15339,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
@@ -15369,7 +15369,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -15399,7 +15399,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -15429,7 +15429,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B430" t="inlineStr"/>
@@ -15459,7 +15459,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -15489,7 +15489,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -15519,7 +15519,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B433" t="inlineStr"/>
@@ -15549,7 +15549,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -15579,7 +15579,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B436" t="inlineStr"/>
@@ -15639,7 +15639,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -15669,7 +15669,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -15699,7 +15699,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B439" t="inlineStr"/>
@@ -15729,7 +15729,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -15789,7 +15789,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -15819,7 +15819,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -15849,7 +15849,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -15879,7 +15879,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B445" t="inlineStr"/>
@@ -15909,7 +15909,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -15939,7 +15939,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -15969,7 +15969,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B448" t="inlineStr"/>
@@ -15999,7 +15999,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -16029,7 +16029,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -16059,7 +16059,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
@@ -16089,7 +16089,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -16119,7 +16119,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -16149,7 +16149,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -16179,7 +16179,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -16209,7 +16209,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -16239,7 +16239,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
@@ -16269,7 +16269,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -16299,7 +16299,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -16329,7 +16329,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B460" t="inlineStr"/>
@@ -16359,7 +16359,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -16389,7 +16389,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -16419,7 +16419,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B463" t="inlineStr"/>
@@ -16449,7 +16449,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -16479,7 +16479,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -16509,7 +16509,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B466" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -16569,7 +16569,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -16599,7 +16599,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B469" t="inlineStr"/>
@@ -16629,7 +16629,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -16659,7 +16659,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -16689,7 +16689,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B472" t="inlineStr"/>
@@ -16719,7 +16719,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -16749,7 +16749,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -16779,7 +16779,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B475" t="inlineStr"/>
@@ -16809,7 +16809,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -16839,7 +16839,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -16869,7 +16869,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B478" t="inlineStr"/>
@@ -16899,7 +16899,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -16929,7 +16929,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -16959,7 +16959,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
@@ -16989,7 +16989,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -17019,7 +17019,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -17049,7 +17049,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B484" t="inlineStr"/>
@@ -17079,7 +17079,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -17109,7 +17109,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -17139,7 +17139,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B487" t="inlineStr"/>
@@ -17169,7 +17169,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -17199,7 +17199,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -17229,7 +17229,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B490" t="inlineStr"/>
@@ -17259,7 +17259,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -17289,7 +17289,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -17319,7 +17319,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B493" t="inlineStr"/>
@@ -17349,7 +17349,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -17379,7 +17379,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -17409,7 +17409,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B496" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -17469,7 +17469,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -17499,7 +17499,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B499" t="inlineStr"/>
@@ -17529,7 +17529,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -17559,7 +17559,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -17589,7 +17589,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -17619,7 +17619,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B503" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -17679,7 +17679,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -17709,7 +17709,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B506" t="inlineStr"/>
@@ -17739,7 +17739,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B508" t="inlineStr"/>
@@ -17799,7 +17799,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B509" t="inlineStr"/>
@@ -17829,7 +17829,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -17859,7 +17859,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B511" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B512" t="inlineStr"/>
@@ -17919,7 +17919,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -17949,7 +17949,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B514" t="inlineStr"/>
@@ -17979,7 +17979,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B515" t="inlineStr"/>
@@ -18009,7 +18009,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -18039,7 +18039,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B517" t="inlineStr"/>
@@ -18069,7 +18069,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B518" t="inlineStr"/>
@@ -18099,7 +18099,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -18129,7 +18129,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B520" t="inlineStr"/>
@@ -18159,7 +18159,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B521" t="inlineStr"/>
@@ -18189,7 +18189,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -18219,7 +18219,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B523" t="inlineStr"/>
@@ -18249,7 +18249,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
@@ -18279,7 +18279,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B525" t="inlineStr"/>
@@ -18309,7 +18309,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -18339,7 +18339,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B527" t="inlineStr"/>
@@ -18369,7 +18369,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -18399,7 +18399,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B529" t="inlineStr"/>
@@ -18429,7 +18429,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
@@ -18459,7 +18459,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -18489,7 +18489,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -18519,7 +18519,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B533" t="inlineStr"/>
@@ -18549,7 +18549,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -18579,7 +18579,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B535" t="inlineStr"/>
@@ -18609,7 +18609,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B536" t="inlineStr"/>
@@ -18639,7 +18639,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -18669,7 +18669,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
@@ -18699,7 +18699,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B539" t="inlineStr"/>
@@ -18729,7 +18729,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -18759,7 +18759,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B541" t="inlineStr"/>
@@ -18789,7 +18789,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B542" t="inlineStr"/>
@@ -18819,7 +18819,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -18849,7 +18849,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B544" t="inlineStr"/>
@@ -18879,7 +18879,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B545" t="inlineStr"/>
@@ -18909,7 +18909,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B547" t="inlineStr"/>
@@ -18969,7 +18969,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B548" t="inlineStr"/>
@@ -18999,7 +18999,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -19029,7 +19029,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B550" t="inlineStr"/>
@@ -19059,7 +19059,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B551" t="inlineStr"/>
@@ -19089,7 +19089,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -19119,7 +19119,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B553" t="inlineStr"/>
@@ -19149,7 +19149,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B554" t="inlineStr"/>
@@ -19179,7 +19179,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -19209,7 +19209,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B556" t="inlineStr"/>
@@ -19239,7 +19239,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B557" t="inlineStr"/>
@@ -19269,7 +19269,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -19299,7 +19299,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B559" t="inlineStr"/>
@@ -19329,7 +19329,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B560" t="inlineStr"/>
@@ -19359,7 +19359,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -19389,7 +19389,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B562" t="inlineStr"/>
@@ -19419,7 +19419,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B563" t="inlineStr"/>
@@ -19449,7 +19449,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -19479,7 +19479,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B565" t="inlineStr"/>
@@ -19509,7 +19509,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B566" t="inlineStr"/>
@@ -19539,7 +19539,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
@@ -19569,7 +19569,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B568" t="inlineStr"/>
@@ -19599,7 +19599,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B569" t="inlineStr"/>
@@ -19629,7 +19629,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B570" t="inlineStr"/>
@@ -19659,7 +19659,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B571" t="inlineStr"/>
@@ -19689,7 +19689,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B572" t="inlineStr"/>
@@ -19719,7 +19719,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B573" t="inlineStr"/>
@@ -19749,7 +19749,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B574" t="inlineStr"/>
@@ -19779,7 +19779,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B575" t="inlineStr"/>
@@ -19809,7 +19809,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
@@ -19839,7 +19839,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B577" t="inlineStr"/>
@@ -19869,7 +19869,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B578" t="inlineStr"/>
@@ -19899,7 +19899,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -19929,7 +19929,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B580" t="inlineStr"/>
@@ -19959,7 +19959,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B581" t="inlineStr"/>
@@ -19989,7 +19989,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
@@ -20019,7 +20019,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B583" t="inlineStr"/>
@@ -20049,7 +20049,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B584" t="inlineStr"/>
@@ -20079,7 +20079,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -20109,7 +20109,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B586" t="inlineStr"/>
@@ -20139,7 +20139,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B587" t="inlineStr"/>
@@ -20169,7 +20169,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -20199,7 +20199,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B589" t="inlineStr"/>
@@ -20229,7 +20229,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B590" t="inlineStr"/>
@@ -20259,7 +20259,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
@@ -20289,7 +20289,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B592" t="inlineStr"/>
@@ -20319,7 +20319,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B593" t="inlineStr"/>
@@ -20349,7 +20349,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B594" t="inlineStr"/>
@@ -20379,7 +20379,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B595" t="inlineStr"/>
@@ -20409,7 +20409,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B596" t="inlineStr"/>
@@ -20439,7 +20439,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
@@ -20469,7 +20469,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B598" t="inlineStr"/>
@@ -20499,7 +20499,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B599" t="inlineStr"/>
@@ -20529,7 +20529,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
@@ -20559,7 +20559,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B601" t="inlineStr"/>
@@ -20589,7 +20589,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B602" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
@@ -20649,7 +20649,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B604" t="inlineStr"/>
@@ -20679,7 +20679,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B605" t="inlineStr"/>
@@ -20709,7 +20709,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
@@ -20739,7 +20739,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B607" t="inlineStr"/>
@@ -20769,7 +20769,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B608" t="inlineStr"/>
@@ -20799,7 +20799,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
@@ -20829,7 +20829,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B610" t="inlineStr"/>
@@ -20859,7 +20859,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B611" t="inlineStr"/>
@@ -20889,7 +20889,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -20919,7 +20919,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B613" t="inlineStr"/>
@@ -20949,7 +20949,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B614" t="inlineStr"/>
@@ -20979,7 +20979,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -21009,7 +21009,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B616" t="inlineStr"/>
@@ -21039,7 +21039,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B617" t="inlineStr"/>
@@ -21069,7 +21069,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -21099,7 +21099,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B619" t="inlineStr"/>
@@ -21129,7 +21129,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B620" t="inlineStr"/>
@@ -21159,7 +21159,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B622" t="inlineStr"/>
@@ -21219,7 +21219,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B623" t="inlineStr"/>
@@ -21249,7 +21249,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
@@ -21279,7 +21279,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B625" t="inlineStr"/>
@@ -21309,7 +21309,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B626" t="inlineStr"/>
@@ -21339,7 +21339,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
@@ -21369,7 +21369,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B628" t="inlineStr"/>
@@ -21399,7 +21399,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B629" t="inlineStr"/>
@@ -21429,7 +21429,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B630" t="inlineStr"/>
@@ -21459,7 +21459,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B631" t="inlineStr"/>
@@ -21489,7 +21489,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B632" t="inlineStr"/>
@@ -21519,7 +21519,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B633" t="inlineStr"/>
@@ -21549,7 +21549,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B634" t="inlineStr"/>
@@ -21579,7 +21579,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B635" t="inlineStr"/>
@@ -21609,7 +21609,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
@@ -21639,7 +21639,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B637" t="inlineStr"/>
@@ -21669,7 +21669,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B638" t="inlineStr"/>
@@ -21699,7 +21699,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B639" t="inlineStr"/>
@@ -21729,7 +21729,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B640" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B641" t="inlineStr"/>
@@ -21789,7 +21789,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
@@ -21819,7 +21819,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B643" t="inlineStr"/>
@@ -21849,7 +21849,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B644" t="inlineStr"/>
@@ -21879,7 +21879,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B645" t="inlineStr"/>
@@ -21909,7 +21909,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B646" t="inlineStr"/>
@@ -21939,7 +21939,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B647" t="inlineStr"/>
@@ -21969,7 +21969,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B648" t="inlineStr"/>
@@ -21999,7 +21999,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B649" t="inlineStr"/>
@@ -22029,7 +22029,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B650" t="inlineStr"/>
@@ -22059,7 +22059,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B651" t="inlineStr"/>
@@ -22089,7 +22089,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B652" t="inlineStr"/>
@@ -22119,7 +22119,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B653" t="inlineStr"/>
@@ -22149,7 +22149,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -22179,7 +22179,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B655" t="inlineStr"/>
@@ -22209,7 +22209,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B656" t="inlineStr"/>
@@ -22239,7 +22239,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -22269,7 +22269,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B658" t="inlineStr"/>
@@ -22299,7 +22299,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B659" t="inlineStr"/>
@@ -22329,7 +22329,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -22359,7 +22359,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B661" t="inlineStr"/>
@@ -22389,7 +22389,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B662" t="inlineStr"/>
@@ -22419,7 +22419,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -22449,7 +22449,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B664" t="inlineStr"/>
@@ -22479,7 +22479,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B665" t="inlineStr"/>
@@ -22509,7 +22509,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B666" t="inlineStr"/>
@@ -22539,7 +22539,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B667" t="inlineStr"/>
@@ -22569,7 +22569,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B668" t="inlineStr"/>
@@ -22599,7 +22599,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B669" t="inlineStr"/>
@@ -22629,7 +22629,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B670" t="inlineStr"/>
@@ -22659,7 +22659,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B671" t="inlineStr"/>
@@ -22689,7 +22689,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B672" t="inlineStr"/>
@@ -22719,7 +22719,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B673" t="inlineStr"/>
@@ -22749,7 +22749,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B674" t="inlineStr"/>
@@ -22779,7 +22779,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B675" t="inlineStr"/>
@@ -22809,7 +22809,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B676" t="inlineStr"/>
@@ -22839,7 +22839,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B677" t="inlineStr"/>
@@ -22869,7 +22869,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
@@ -22899,7 +22899,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B679" t="inlineStr"/>
@@ -22929,7 +22929,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B680" t="inlineStr"/>
@@ -22959,7 +22959,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
@@ -22989,7 +22989,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B682" t="inlineStr"/>
@@ -23019,7 +23019,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B683" t="inlineStr"/>
@@ -23049,7 +23049,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
@@ -23079,7 +23079,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B685" t="inlineStr"/>
@@ -23109,7 +23109,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B686" t="inlineStr"/>
@@ -23139,7 +23139,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
@@ -23169,7 +23169,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B688" t="inlineStr"/>
@@ -23199,7 +23199,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B689" t="inlineStr"/>
@@ -23229,7 +23229,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -23259,7 +23259,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B691" t="inlineStr"/>
@@ -23289,7 +23289,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B692" t="inlineStr"/>
@@ -23319,7 +23319,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -23349,7 +23349,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B694" t="inlineStr"/>
@@ -23379,7 +23379,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B695" t="inlineStr"/>
@@ -23409,7 +23409,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B696" t="inlineStr"/>
@@ -23439,7 +23439,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B697" t="inlineStr"/>
@@ -23469,7 +23469,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B698" t="inlineStr"/>
@@ -23499,7 +23499,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B699" t="inlineStr"/>
@@ -23529,7 +23529,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B700" t="inlineStr"/>
@@ -23559,7 +23559,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B701" t="inlineStr"/>
@@ -23589,7 +23589,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -23619,7 +23619,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B703" t="inlineStr"/>
@@ -23649,7 +23649,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B704" t="inlineStr"/>
@@ -23679,7 +23679,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B705" t="inlineStr"/>
@@ -23709,7 +23709,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B706" t="inlineStr"/>
@@ -23739,7 +23739,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B707" t="inlineStr"/>
@@ -23769,7 +23769,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B708" t="inlineStr"/>
@@ -23799,7 +23799,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B709" t="inlineStr"/>
@@ -23829,7 +23829,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B710" t="inlineStr"/>
@@ -23859,7 +23859,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B711" t="inlineStr"/>
@@ -23889,7 +23889,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B712" t="inlineStr"/>
@@ -23919,7 +23919,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B713" t="inlineStr"/>
@@ -23949,7 +23949,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B714" t="inlineStr"/>
@@ -23979,7 +23979,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B715" t="inlineStr"/>
@@ -24009,7 +24009,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B716" t="inlineStr"/>
@@ -24039,7 +24039,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
@@ -24069,7 +24069,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B718" t="inlineStr"/>
@@ -24099,7 +24099,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B719" t="inlineStr"/>
@@ -24129,7 +24129,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
@@ -24159,7 +24159,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B721" t="inlineStr"/>
@@ -24189,7 +24189,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B722" t="inlineStr"/>
@@ -24219,7 +24219,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
@@ -24249,7 +24249,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B724" t="inlineStr"/>
@@ -24279,7 +24279,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B725" t="inlineStr"/>
@@ -24309,7 +24309,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B726" t="inlineStr"/>
@@ -24339,7 +24339,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B727" t="inlineStr"/>
@@ -24369,7 +24369,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B728" t="inlineStr"/>
@@ -24399,7 +24399,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B729" t="inlineStr"/>
@@ -24429,7 +24429,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Cross-strain baseline</t>
+          <t>Different strain, different peptide</t>
         </is>
       </c>
       <c r="B730" t="inlineStr"/>

--- a/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
+++ b/Final_Figures_and_Sheets_Singleset/Kb_pc_values_FullAlpha.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J734"/>
+  <dimension ref="A1:I734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>Pair</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Tissue</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -518,7 +513,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -558,7 +552,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -598,7 +591,6 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -638,7 +630,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -678,7 +669,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -718,7 +708,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -758,7 +747,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -798,7 +786,6 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -838,7 +825,6 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,7 +864,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -918,7 +903,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -958,7 +942,6 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -998,7 +981,6 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1038,7 +1020,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1078,7 +1059,6 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1118,7 +1098,6 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1158,7 +1137,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1198,7 +1176,6 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1238,7 +1215,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1278,7 +1254,6 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1318,7 +1293,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1358,7 +1332,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1398,7 +1371,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1438,7 +1410,6 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1478,7 +1449,6 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1518,7 +1488,6 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1558,7 +1527,6 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1596,11 +1564,6 @@
           <t>(1,2)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1638,11 +1601,6 @@
           <t>(1,3)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1680,11 +1638,6 @@
           <t>(1,4)</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1722,11 +1675,6 @@
           <t>(1,5)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1764,11 +1712,6 @@
           <t>(1,6)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1806,11 +1749,6 @@
           <t>(2,3)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1848,11 +1786,6 @@
           <t>(2,4)</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1890,11 +1823,6 @@
           <t>(2,5)</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1932,11 +1860,6 @@
           <t>(2,6)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1974,11 +1897,6 @@
           <t>(3,4)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2016,11 +1934,6 @@
           <t>(3,5)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2058,11 +1971,6 @@
           <t>(3,6)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2100,11 +2008,6 @@
           <t>(4,5)</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2142,11 +2045,6 @@
           <t>(4,6)</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2184,11 +2082,6 @@
           <t>(5,6)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2226,11 +2119,6 @@
           <t>(7,8)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2268,11 +2156,6 @@
           <t>(7,9)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2310,11 +2193,6 @@
           <t>(8,9)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2352,11 +2230,6 @@
           <t>(10,11)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2394,11 +2267,6 @@
           <t>(10,12)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2436,11 +2304,6 @@
           <t>(10,13)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2478,11 +2341,6 @@
           <t>(10,14)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2520,11 +2378,6 @@
           <t>(10,15)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2562,11 +2415,6 @@
           <t>(11,12)</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2604,11 +2452,6 @@
           <t>(11,13)</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2646,11 +2489,6 @@
           <t>(11,14)</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2688,11 +2526,6 @@
           <t>(11,15)</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2730,11 +2563,6 @@
           <t>(12,13)</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2772,11 +2600,6 @@
           <t>(12,14)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2814,11 +2637,6 @@
           <t>(12,15)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2856,11 +2674,6 @@
           <t>(13,14)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2898,11 +2711,6 @@
           <t>(13,15)</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2940,11 +2748,6 @@
           <t>(14,15)</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2982,11 +2785,6 @@
           <t>(16,17)</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3024,11 +2822,6 @@
           <t>(16,18)</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3066,11 +2859,6 @@
           <t>(17,18)</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3108,11 +2896,6 @@
           <t>(19,20)</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3150,11 +2933,6 @@
           <t>(19,21)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3192,11 +2970,6 @@
           <t>(19,22)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3234,11 +3007,6 @@
           <t>(19,23)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3276,11 +3044,6 @@
           <t>(19,24)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3318,11 +3081,6 @@
           <t>(20,21)</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3360,11 +3118,6 @@
           <t>(20,22)</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3402,11 +3155,6 @@
           <t>(20,23)</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3444,11 +3192,6 @@
           <t>(20,24)</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3486,11 +3229,6 @@
           <t>(21,22)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3528,11 +3266,6 @@
           <t>(21,23)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3570,11 +3303,6 @@
           <t>(21,24)</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3612,11 +3340,6 @@
           <t>(22,23)</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3654,11 +3377,6 @@
           <t>(22,24)</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3696,11 +3414,6 @@
           <t>(23,24)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3738,11 +3451,6 @@
           <t>(25,26)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3780,11 +3488,6 @@
           <t>(25,27)</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3820,11 +3523,6 @@
       <c r="I82" t="inlineStr">
         <is>
           <t>(26,27)</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3558,6 @@
           <t>(1,2)</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3894,7 +3591,6 @@
           <t>(1,3)</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3928,7 +3624,6 @@
           <t>(1,4)</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3962,7 +3657,6 @@
           <t>(1,5)</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3996,7 +3690,6 @@
           <t>(1,6)</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4030,7 +3723,6 @@
           <t>(1,7)</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4064,7 +3756,6 @@
           <t>(1,8)</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4098,7 +3789,6 @@
           <t>(1,9)</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4132,7 +3822,6 @@
           <t>(2,3)</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4166,7 +3855,6 @@
           <t>(2,4)</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4200,7 +3888,6 @@
           <t>(2,5)</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4234,7 +3921,6 @@
           <t>(2,6)</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4268,7 +3954,6 @@
           <t>(2,7)</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4302,7 +3987,6 @@
           <t>(2,8)</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4336,7 +4020,6 @@
           <t>(2,9)</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4370,7 +4053,6 @@
           <t>(3,4)</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4404,7 +4086,6 @@
           <t>(3,5)</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4438,7 +4119,6 @@
           <t>(3,6)</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4472,7 +4152,6 @@
           <t>(3,7)</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4506,7 +4185,6 @@
           <t>(3,8)</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4540,7 +4218,6 @@
           <t>(3,9)</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4574,7 +4251,6 @@
           <t>(4,5)</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4608,7 +4284,6 @@
           <t>(4,6)</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4642,7 +4317,6 @@
           <t>(4,7)</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4676,7 +4350,6 @@
           <t>(4,8)</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4710,7 +4383,6 @@
           <t>(4,9)</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4744,7 +4416,6 @@
           <t>(5,6)</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4778,7 +4449,6 @@
           <t>(5,7)</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4812,7 +4482,6 @@
           <t>(5,8)</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4846,7 +4515,6 @@
           <t>(5,9)</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4880,7 +4548,6 @@
           <t>(6,7)</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4914,7 +4581,6 @@
           <t>(6,8)</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4948,7 +4614,6 @@
           <t>(6,9)</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4982,7 +4647,6 @@
           <t>(7,8)</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5016,7 +4680,6 @@
           <t>(7,9)</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5050,7 +4713,6 @@
           <t>(8,9)</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5084,7 +4746,6 @@
           <t>(10,11)</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5118,7 +4779,6 @@
           <t>(10,12)</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5152,7 +4812,6 @@
           <t>(10,13)</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5186,7 +4845,6 @@
           <t>(10,14)</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5220,7 +4878,6 @@
           <t>(10,15)</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5254,7 +4911,6 @@
           <t>(10,16)</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5288,7 +4944,6 @@
           <t>(10,17)</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5322,7 +4977,6 @@
           <t>(10,18)</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5356,7 +5010,6 @@
           <t>(11,12)</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5390,7 +5043,6 @@
           <t>(11,13)</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5424,7 +5076,6 @@
           <t>(11,14)</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5458,7 +5109,6 @@
           <t>(11,15)</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5492,7 +5142,6 @@
           <t>(11,16)</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5526,7 +5175,6 @@
           <t>(11,17)</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5560,7 +5208,6 @@
           <t>(11,18)</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5594,7 +5241,6 @@
           <t>(12,13)</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5628,7 +5274,6 @@
           <t>(12,14)</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5662,7 +5307,6 @@
           <t>(12,15)</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5696,7 +5340,6 @@
           <t>(12,16)</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5730,7 +5373,6 @@
           <t>(12,17)</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5764,7 +5406,6 @@
           <t>(12,18)</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5798,7 +5439,6 @@
           <t>(13,14)</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5832,7 +5472,6 @@
           <t>(13,15)</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5866,7 +5505,6 @@
           <t>(13,16)</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5900,7 +5538,6 @@
           <t>(13,17)</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5934,7 +5571,6 @@
           <t>(13,18)</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5968,7 +5604,6 @@
           <t>(14,15)</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6002,7 +5637,6 @@
           <t>(14,16)</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6036,7 +5670,6 @@
           <t>(14,17)</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6070,7 +5703,6 @@
           <t>(14,18)</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6104,7 +5736,6 @@
           <t>(15,16)</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6138,7 +5769,6 @@
           <t>(15,17)</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6172,7 +5802,6 @@
           <t>(15,18)</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6206,7 +5835,6 @@
           <t>(16,17)</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6240,7 +5868,6 @@
           <t>(16,18)</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6274,7 +5901,6 @@
           <t>(17,18)</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6308,7 +5934,6 @@
           <t>(19,20)</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6342,7 +5967,6 @@
           <t>(19,21)</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6376,7 +6000,6 @@
           <t>(19,22)</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6410,7 +6033,6 @@
           <t>(19,23)</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6444,7 +6066,6 @@
           <t>(19,24)</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6478,7 +6099,6 @@
           <t>(19,25)</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6512,7 +6132,6 @@
           <t>(19,26)</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6546,7 +6165,6 @@
           <t>(19,27)</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6580,7 +6198,6 @@
           <t>(20,21)</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6614,7 +6231,6 @@
           <t>(20,22)</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6648,7 +6264,6 @@
           <t>(20,23)</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6682,7 +6297,6 @@
           <t>(20,24)</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6716,7 +6330,6 @@
           <t>(20,25)</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6750,7 +6363,6 @@
           <t>(20,26)</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6784,7 +6396,6 @@
           <t>(20,27)</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6818,7 +6429,6 @@
           <t>(21,22)</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6852,7 +6462,6 @@
           <t>(21,23)</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6886,7 +6495,6 @@
           <t>(21,24)</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6920,7 +6528,6 @@
           <t>(21,25)</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6954,7 +6561,6 @@
           <t>(21,26)</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6988,7 +6594,6 @@
           <t>(21,27)</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7022,7 +6627,6 @@
           <t>(22,23)</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7056,7 +6660,6 @@
           <t>(22,24)</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7090,7 +6693,6 @@
           <t>(22,25)</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7124,7 +6726,6 @@
           <t>(22,26)</t>
         </is>
       </c>
-      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7158,7 +6759,6 @@
           <t>(22,27)</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7192,7 +6792,6 @@
           <t>(23,24)</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7226,7 +6825,6 @@
           <t>(23,25)</t>
         </is>
       </c>
-      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7260,7 +6858,6 @@
           <t>(23,26)</t>
         </is>
       </c>
-      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7294,7 +6891,6 @@
           <t>(23,27)</t>
         </is>
       </c>
-      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7328,7 +6924,6 @@
           <t>(24,25)</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7362,7 +6957,6 @@
           <t>(24,26)</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7396,7 +6990,6 @@
           <t>(24,27)</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7430,7 +7023,6 @@
           <t>(25,26)</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7464,7 +7056,6 @@
           <t>(25,27)</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7498,7 +7089,6 @@
           <t>(26,27)</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7532,7 +7122,6 @@
           <t>(1,2)</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7566,7 +7155,6 @@
           <t>(1,3)</t>
         </is>
       </c>
-      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7600,7 +7188,6 @@
           <t>(1,4)</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7634,7 +7221,6 @@
           <t>(1,5)</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7668,7 +7254,6 @@
           <t>(1,6)</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7702,7 +7287,6 @@
           <t>(1,10)</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7736,7 +7320,6 @@
           <t>(1,11)</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7770,7 +7353,6 @@
           <t>(1,12)</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7804,7 +7386,6 @@
           <t>(1,13)</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7838,7 +7419,6 @@
           <t>(1,14)</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7872,7 +7452,6 @@
           <t>(1,15)</t>
         </is>
       </c>
-      <c r="J201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7906,7 +7485,6 @@
           <t>(1,19)</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7940,7 +7518,6 @@
           <t>(1,20)</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7974,7 +7551,6 @@
           <t>(1,21)</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8008,7 +7584,6 @@
           <t>(1,22)</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8042,7 +7617,6 @@
           <t>(1,23)</t>
         </is>
       </c>
-      <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8076,7 +7650,6 @@
           <t>(1,24)</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8110,7 +7683,6 @@
           <t>(2,3)</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8144,7 +7716,6 @@
           <t>(2,4)</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8178,7 +7749,6 @@
           <t>(2,5)</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8212,7 +7782,6 @@
           <t>(2,6)</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8246,7 +7815,6 @@
           <t>(2,10)</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8280,7 +7848,6 @@
           <t>(2,11)</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8314,7 +7881,6 @@
           <t>(2,12)</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8348,7 +7914,6 @@
           <t>(2,13)</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8382,7 +7947,6 @@
           <t>(2,14)</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8416,7 +7980,6 @@
           <t>(2,15)</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8450,7 +8013,6 @@
           <t>(2,19)</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8484,7 +8046,6 @@
           <t>(2,20)</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8518,7 +8079,6 @@
           <t>(2,21)</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8552,7 +8112,6 @@
           <t>(2,22)</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8586,7 +8145,6 @@
           <t>(2,23)</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8620,7 +8178,6 @@
           <t>(2,24)</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8654,7 +8211,6 @@
           <t>(3,4)</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8688,7 +8244,6 @@
           <t>(3,5)</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8722,7 +8277,6 @@
           <t>(3,6)</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8756,7 +8310,6 @@
           <t>(3,10)</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8790,7 +8343,6 @@
           <t>(3,11)</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8824,7 +8376,6 @@
           <t>(3,12)</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8858,7 +8409,6 @@
           <t>(3,13)</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8892,7 +8442,6 @@
           <t>(3,14)</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8926,7 +8475,6 @@
           <t>(3,15)</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8960,7 +8508,6 @@
           <t>(3,19)</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8994,7 +8541,6 @@
           <t>(3,20)</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9028,7 +8574,6 @@
           <t>(3,21)</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9062,7 +8607,6 @@
           <t>(3,22)</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9096,7 +8640,6 @@
           <t>(3,23)</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9130,7 +8673,6 @@
           <t>(3,24)</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9164,7 +8706,6 @@
           <t>(4,5)</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9198,7 +8739,6 @@
           <t>(4,6)</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9232,7 +8772,6 @@
           <t>(4,10)</t>
         </is>
       </c>
-      <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9266,7 +8805,6 @@
           <t>(4,11)</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9300,7 +8838,6 @@
           <t>(4,12)</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9334,7 +8871,6 @@
           <t>(4,13)</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9368,7 +8904,6 @@
           <t>(4,14)</t>
         </is>
       </c>
-      <c r="J245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9402,7 +8937,6 @@
           <t>(4,15)</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9436,7 +8970,6 @@
           <t>(4,19)</t>
         </is>
       </c>
-      <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9470,7 +9003,6 @@
           <t>(4,20)</t>
         </is>
       </c>
-      <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9504,7 +9036,6 @@
           <t>(4,21)</t>
         </is>
       </c>
-      <c r="J249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9538,7 +9069,6 @@
           <t>(4,22)</t>
         </is>
       </c>
-      <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9572,7 +9102,6 @@
           <t>(4,23)</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9606,7 +9135,6 @@
           <t>(4,24)</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9640,7 +9168,6 @@
           <t>(5,6)</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9674,7 +9201,6 @@
           <t>(5,10)</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9708,7 +9234,6 @@
           <t>(5,11)</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9742,7 +9267,6 @@
           <t>(5,12)</t>
         </is>
       </c>
-      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9776,7 +9300,6 @@
           <t>(5,13)</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9810,7 +9333,6 @@
           <t>(5,14)</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9844,7 +9366,6 @@
           <t>(5,15)</t>
         </is>
       </c>
-      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9878,7 +9399,6 @@
           <t>(5,19)</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9912,7 +9432,6 @@
           <t>(5,20)</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9946,7 +9465,6 @@
           <t>(5,21)</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9980,7 +9498,6 @@
           <t>(5,22)</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -10014,7 +9531,6 @@
           <t>(5,23)</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -10048,7 +9564,6 @@
           <t>(5,24)</t>
         </is>
       </c>
-      <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10082,7 +9597,6 @@
           <t>(6,10)</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10116,7 +9630,6 @@
           <t>(6,11)</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10150,7 +9663,6 @@
           <t>(6,12)</t>
         </is>
       </c>
-      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -10184,7 +9696,6 @@
           <t>(6,13)</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -10218,7 +9729,6 @@
           <t>(6,14)</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -10252,7 +9762,6 @@
           <t>(6,15)</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -10286,7 +9795,6 @@
           <t>(6,19)</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -10320,7 +9828,6 @@
           <t>(6,20)</t>
         </is>
       </c>
-      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -10354,7 +9861,6 @@
           <t>(6,21)</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10388,7 +9894,6 @@
           <t>(6,22)</t>
         </is>
       </c>
-      <c r="J275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10422,7 +9927,6 @@
           <t>(6,23)</t>
         </is>
       </c>
-      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -10456,7 +9960,6 @@
           <t>(6,24)</t>
         </is>
       </c>
-      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -10490,7 +9993,6 @@
           <t>(10,11)</t>
         </is>
       </c>
-      <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -10524,7 +10026,6 @@
           <t>(10,12)</t>
         </is>
       </c>
-      <c r="J279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10558,7 +10059,6 @@
           <t>(10,13)</t>
         </is>
       </c>
-      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -10592,7 +10092,6 @@
           <t>(10,14)</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -10626,7 +10125,6 @@
           <t>(10,15)</t>
         </is>
       </c>
-      <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -10660,7 +10158,6 @@
           <t>(10,19)</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -10694,7 +10191,6 @@
           <t>(10,20)</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -10728,7 +10224,6 @@
           <t>(10,21)</t>
         </is>
       </c>
-      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -10762,7 +10257,6 @@
           <t>(10,22)</t>
         </is>
       </c>
-      <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -10796,7 +10290,6 @@
           <t>(10,23)</t>
         </is>
       </c>
-      <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -10830,7 +10323,6 @@
           <t>(10,24)</t>
         </is>
       </c>
-      <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -10864,7 +10356,6 @@
           <t>(11,12)</t>
         </is>
       </c>
-      <c r="J289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10898,7 +10389,6 @@
           <t>(11,13)</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10932,7 +10422,6 @@
           <t>(11,14)</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10966,7 +10455,6 @@
           <t>(11,15)</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -11000,7 +10488,6 @@
           <t>(11,19)</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -11034,7 +10521,6 @@
           <t>(11,20)</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11068,7 +10554,6 @@
           <t>(11,21)</t>
         </is>
       </c>
-      <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11102,7 +10587,6 @@
           <t>(11,22)</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11136,7 +10620,6 @@
           <t>(11,23)</t>
         </is>
       </c>
-      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11170,7 +10653,6 @@
           <t>(11,24)</t>
         </is>
       </c>
-      <c r="J298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11204,7 +10686,6 @@
           <t>(12,13)</t>
         </is>
       </c>
-      <c r="J299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -11238,7 +10719,6 @@
           <t>(12,14)</t>
         </is>
       </c>
-      <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -11272,7 +10752,6 @@
           <t>(12,15)</t>
         </is>
       </c>
-      <c r="J301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -11306,7 +10785,6 @@
           <t>(12,19)</t>
         </is>
       </c>
-      <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11340,7 +10818,6 @@
           <t>(12,20)</t>
         </is>
       </c>
-      <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11374,7 +10851,6 @@
           <t>(12,21)</t>
         </is>
       </c>
-      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11408,7 +10884,6 @@
           <t>(12,22)</t>
         </is>
       </c>
-      <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11442,7 +10917,6 @@
           <t>(12,23)</t>
         </is>
       </c>
-      <c r="J306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -11476,7 +10950,6 @@
           <t>(12,24)</t>
         </is>
       </c>
-      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -11510,7 +10983,6 @@
           <t>(13,14)</t>
         </is>
       </c>
-      <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -11544,7 +11016,6 @@
           <t>(13,15)</t>
         </is>
       </c>
-      <c r="J309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -11578,7 +11049,6 @@
           <t>(13,19)</t>
         </is>
       </c>
-      <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -11612,7 +11082,6 @@
           <t>(13,20)</t>
         </is>
       </c>
-      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -11646,7 +11115,6 @@
           <t>(13,21)</t>
         </is>
       </c>
-      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -11680,7 +11148,6 @@
           <t>(13,22)</t>
         </is>
       </c>
-      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -11714,7 +11181,6 @@
           <t>(13,23)</t>
         </is>
       </c>
-      <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -11748,7 +11214,6 @@
           <t>(13,24)</t>
         </is>
       </c>
-      <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -11782,7 +11247,6 @@
           <t>(14,15)</t>
         </is>
       </c>
-      <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -11816,7 +11280,6 @@
           <t>(14,19)</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -11850,7 +11313,6 @@
           <t>(14,20)</t>
         </is>
       </c>
-      <c r="J318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -11884,7 +11346,6 @@
           <t>(14,21)</t>
         </is>
       </c>
-      <c r="J319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -11918,7 +11379,6 @@
           <t>(14,22)</t>
         </is>
       </c>
-      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11952,7 +11412,6 @@
           <t>(14,23)</t>
         </is>
       </c>
-      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11986,7 +11445,6 @@
           <t>(14,24)</t>
         </is>
       </c>
-      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12020,7 +11478,6 @@
           <t>(15,19)</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12054,7 +11511,6 @@
           <t>(15,20)</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12088,7 +11544,6 @@
           <t>(15,21)</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -12122,7 +11577,6 @@
           <t>(15,22)</t>
         </is>
       </c>
-      <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12156,7 +11610,6 @@
           <t>(15,23)</t>
         </is>
       </c>
-      <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12190,7 +11643,6 @@
           <t>(15,24)</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12224,7 +11676,6 @@
           <t>(19,20)</t>
         </is>
       </c>
-      <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -12258,7 +11709,6 @@
           <t>(19,21)</t>
         </is>
       </c>
-      <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12292,7 +11742,6 @@
           <t>(19,22)</t>
         </is>
       </c>
-      <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -12326,7 +11775,6 @@
           <t>(19,23)</t>
         </is>
       </c>
-      <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12360,7 +11808,6 @@
           <t>(19,24)</t>
         </is>
       </c>
-      <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -12394,7 +11841,6 @@
           <t>(20,21)</t>
         </is>
       </c>
-      <c r="J334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -12428,7 +11874,6 @@
           <t>(20,22)</t>
         </is>
       </c>
-      <c r="J335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -12462,7 +11907,6 @@
           <t>(20,23)</t>
         </is>
       </c>
-      <c r="J336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -12496,7 +11940,6 @@
           <t>(20,24)</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -12530,7 +11973,6 @@
           <t>(21,22)</t>
         </is>
       </c>
-      <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -12564,7 +12006,6 @@
           <t>(21,23)</t>
         </is>
       </c>
-      <c r="J339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -12598,7 +12039,6 @@
           <t>(21,24)</t>
         </is>
       </c>
-      <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -12632,7 +12072,6 @@
           <t>(22,23)</t>
         </is>
       </c>
-      <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -12666,7 +12105,6 @@
           <t>(22,24)</t>
         </is>
       </c>
-      <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -12700,7 +12138,6 @@
           <t>(23,24)</t>
         </is>
       </c>
-      <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -12734,7 +12171,6 @@
           <t>(7,8)</t>
         </is>
       </c>
-      <c r="J344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -12768,7 +12204,6 @@
           <t>(7,9)</t>
         </is>
       </c>
-      <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -12802,7 +12237,6 @@
           <t>(7,16)</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -12836,7 +12270,6 @@
           <t>(7,17)</t>
         </is>
       </c>
-      <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -12870,7 +12303,6 @@
           <t>(7,18)</t>
         </is>
       </c>
-      <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -12904,7 +12336,6 @@
           <t>(7,25)</t>
         </is>
       </c>
-      <c r="J349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -12938,7 +12369,6 @@
           <t>(7,26)</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12972,7 +12402,6 @@
           <t>(7,27)</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13006,7 +12435,6 @@
           <t>(8,9)</t>
         </is>
       </c>
-      <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13040,7 +12468,6 @@
           <t>(8,16)</t>
         </is>
       </c>
-      <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -13074,7 +12501,6 @@
           <t>(8,17)</t>
         </is>
       </c>
-      <c r="J354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -13108,7 +12534,6 @@
           <t>(8,18)</t>
         </is>
       </c>
-      <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -13142,7 +12567,6 @@
           <t>(8,25)</t>
         </is>
       </c>
-      <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -13176,7 +12600,6 @@
           <t>(8,26)</t>
         </is>
       </c>
-      <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -13210,7 +12633,6 @@
           <t>(8,27)</t>
         </is>
       </c>
-      <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13244,7 +12666,6 @@
           <t>(9,16)</t>
         </is>
       </c>
-      <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13278,7 +12699,6 @@
           <t>(9,17)</t>
         </is>
       </c>
-      <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -13312,7 +12732,6 @@
           <t>(9,18)</t>
         </is>
       </c>
-      <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -13346,7 +12765,6 @@
           <t>(9,25)</t>
         </is>
       </c>
-      <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -13380,7 +12798,6 @@
           <t>(9,26)</t>
         </is>
       </c>
-      <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -13414,7 +12831,6 @@
           <t>(9,27)</t>
         </is>
       </c>
-      <c r="J364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -13448,7 +12864,6 @@
           <t>(16,17)</t>
         </is>
       </c>
-      <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -13482,7 +12897,6 @@
           <t>(16,18)</t>
         </is>
       </c>
-      <c r="J366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -13516,7 +12930,6 @@
           <t>(16,25)</t>
         </is>
       </c>
-      <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -13550,7 +12963,6 @@
           <t>(16,26)</t>
         </is>
       </c>
-      <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -13584,7 +12996,6 @@
           <t>(16,27)</t>
         </is>
       </c>
-      <c r="J369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -13618,7 +13029,6 @@
           <t>(17,18)</t>
         </is>
       </c>
-      <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -13652,7 +13062,6 @@
           <t>(17,25)</t>
         </is>
       </c>
-      <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -13686,7 +13095,6 @@
           <t>(17,26)</t>
         </is>
       </c>
-      <c r="J372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -13720,7 +13128,6 @@
           <t>(17,27)</t>
         </is>
       </c>
-      <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -13754,7 +13161,6 @@
           <t>(18,25)</t>
         </is>
       </c>
-      <c r="J374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -13788,7 +13194,6 @@
           <t>(18,26)</t>
         </is>
       </c>
-      <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -13822,7 +13227,6 @@
           <t>(18,27)</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -13856,7 +13260,6 @@
           <t>(25,26)</t>
         </is>
       </c>
-      <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -13890,7 +13293,6 @@
           <t>(25,27)</t>
         </is>
       </c>
-      <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -13924,7 +13326,6 @@
           <t>(26,27)</t>
         </is>
       </c>
-      <c r="J379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -13954,7 +13355,6 @@
           <t>(1,2)</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13984,7 +13384,6 @@
           <t>(1,3)</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14014,7 +13413,6 @@
           <t>(1,4)</t>
         </is>
       </c>
-      <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14044,7 +13442,6 @@
           <t>(1,5)</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -14074,7 +13471,6 @@
           <t>(1,6)</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14104,7 +13500,6 @@
           <t>(1,7)</t>
         </is>
       </c>
-      <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -14134,7 +13529,6 @@
           <t>(1,8)</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -14164,7 +13558,6 @@
           <t>(1,9)</t>
         </is>
       </c>
-      <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -14194,7 +13587,6 @@
           <t>(1,10)</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -14224,7 +13616,6 @@
           <t>(1,11)</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -14254,7 +13645,6 @@
           <t>(1,12)</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -14284,7 +13674,6 @@
           <t>(1,13)</t>
         </is>
       </c>
-      <c r="J391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -14314,7 +13703,6 @@
           <t>(1,14)</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -14344,7 +13732,6 @@
           <t>(1,15)</t>
         </is>
       </c>
-      <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -14374,7 +13761,6 @@
           <t>(1,16)</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -14404,7 +13790,6 @@
           <t>(1,17)</t>
         </is>
       </c>
-      <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -14434,7 +13819,6 @@
           <t>(1,18)</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -14464,7 +13848,6 @@
           <t>(1,19)</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -14494,7 +13877,6 @@
           <t>(1,20)</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -14524,7 +13906,6 @@
           <t>(1,21)</t>
         </is>
       </c>
-      <c r="J399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -14554,7 +13935,6 @@
           <t>(1,22)</t>
         </is>
       </c>
-      <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -14584,7 +13964,6 @@
           <t>(1,23)</t>
         </is>
       </c>
-      <c r="J401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -14614,7 +13993,6 @@
           <t>(1,24)</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -14644,7 +14022,6 @@
           <t>(1,25)</t>
         </is>
       </c>
-      <c r="J403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -14674,7 +14051,6 @@
           <t>(1,26)</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -14704,7 +14080,6 @@
           <t>(1,27)</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -14734,7 +14109,6 @@
           <t>(2,3)</t>
         </is>
       </c>
-      <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -14764,7 +14138,6 @@
           <t>(2,4)</t>
         </is>
       </c>
-      <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -14794,7 +14167,6 @@
           <t>(2,5)</t>
         </is>
       </c>
-      <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -14824,7 +14196,6 @@
           <t>(2,6)</t>
         </is>
       </c>
-      <c r="J409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -14854,7 +14225,6 @@
           <t>(2,7)</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14884,7 +14254,6 @@
           <t>(2,8)</t>
         </is>
       </c>
-      <c r="J411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14914,7 +14283,6 @@
           <t>(2,9)</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14944,7 +14312,6 @@
           <t>(2,10)</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14974,7 +14341,6 @@
           <t>(2,11)</t>
         </is>
       </c>
-      <c r="J414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -15004,7 +14370,6 @@
           <t>(2,12)</t>
         </is>
       </c>
-      <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -15034,7 +14399,6 @@
           <t>(2,13)</t>
         </is>
       </c>
-      <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -15064,7 +14428,6 @@
           <t>(2,14)</t>
         </is>
       </c>
-      <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -15094,7 +14457,6 @@
           <t>(2,15)</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -15124,7 +14486,6 @@
           <t>(2,16)</t>
         </is>
       </c>
-      <c r="J419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -15154,7 +14515,6 @@
           <t>(2,17)</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -15184,7 +14544,6 @@
           <t>(2,18)</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -15214,7 +14573,6 @@
           <t>(2,19)</t>
         </is>
       </c>
-      <c r="J422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -15244,7 +14602,6 @@
           <t>(2,20)</t>
         </is>
       </c>
-      <c r="J423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -15274,7 +14631,6 @@
           <t>(2,21)</t>
         </is>
       </c>
-      <c r="J424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -15304,7 +14660,6 @@
           <t>(2,22)</t>
         </is>
       </c>
-      <c r="J425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -15334,7 +14689,6 @@
           <t>(2,23)</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -15364,7 +14718,6 @@
           <t>(2,24)</t>
         </is>
       </c>
-      <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -15394,7 +14747,6 @@
           <t>(2,25)</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -15424,7 +14776,6 @@
           <t>(2,26)</t>
         </is>
       </c>
-      <c r="J429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -15454,7 +14805,6 @@
           <t>(2,27)</t>
         </is>
       </c>
-      <c r="J430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -15484,7 +14834,6 @@
           <t>(3,4)</t>
         </is>
       </c>
-      <c r="J431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -15514,7 +14863,6 @@
           <t>(3,5)</t>
         </is>
       </c>
-      <c r="J432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -15544,7 +14892,6 @@
           <t>(3,6)</t>
         </is>
       </c>
-      <c r="J433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -15574,7 +14921,6 @@
           <t>(3,7)</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -15604,7 +14950,6 @@
           <t>(3,8)</t>
         </is>
       </c>
-      <c r="J435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -15634,7 +14979,6 @@
           <t>(3,9)</t>
         </is>
       </c>
-      <c r="J436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -15664,7 +15008,6 @@
           <t>(3,10)</t>
         </is>
       </c>
-      <c r="J437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -15694,7 +15037,6 @@
           <t>(3,11)</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -15724,7 +15066,6 @@
           <t>(3,12)</t>
         </is>
       </c>
-      <c r="J439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -15754,7 +15095,6 @@
           <t>(3,13)</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -15784,7 +15124,6 @@
           <t>(3,14)</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -15814,7 +15153,6 @@
           <t>(3,15)</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -15844,7 +15182,6 @@
           <t>(3,16)</t>
         </is>
       </c>
-      <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -15874,7 +15211,6 @@
           <t>(3,17)</t>
         </is>
       </c>
-      <c r="J444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -15904,7 +15240,6 @@
           <t>(3,18)</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -15934,7 +15269,6 @@
           <t>(3,19)</t>
         </is>
       </c>
-      <c r="J446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -15964,7 +15298,6 @@
           <t>(3,20)</t>
         </is>
       </c>
-      <c r="J447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -15994,7 +15327,6 @@
           <t>(3,21)</t>
         </is>
       </c>
-      <c r="J448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -16024,7 +15356,6 @@
           <t>(3,22)</t>
         </is>
       </c>
-      <c r="J449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -16054,7 +15385,6 @@
           <t>(3,23)</t>
         </is>
       </c>
-      <c r="J450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -16084,7 +15414,6 @@
           <t>(3,24)</t>
         </is>
       </c>
-      <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -16114,7 +15443,6 @@
           <t>(3,25)</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -16144,7 +15472,6 @@
           <t>(3,26)</t>
         </is>
       </c>
-      <c r="J453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -16174,7 +15501,6 @@
           <t>(3,27)</t>
         </is>
       </c>
-      <c r="J454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -16204,7 +15530,6 @@
           <t>(4,5)</t>
         </is>
       </c>
-      <c r="J455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -16234,7 +15559,6 @@
           <t>(4,6)</t>
         </is>
       </c>
-      <c r="J456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -16264,7 +15588,6 @@
           <t>(4,7)</t>
         </is>
       </c>
-      <c r="J457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -16294,7 +15617,6 @@
           <t>(4,8)</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -16324,7 +15646,6 @@
           <t>(4,9)</t>
         </is>
       </c>
-      <c r="J459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -16354,7 +15675,6 @@
           <t>(4,10)</t>
         </is>
       </c>
-      <c r="J460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -16384,7 +15704,6 @@
           <t>(4,11)</t>
         </is>
       </c>
-      <c r="J461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -16414,7 +15733,6 @@
           <t>(4,12)</t>
         </is>
       </c>
-      <c r="J462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -16444,7 +15762,6 @@
           <t>(4,13)</t>
         </is>
       </c>
-      <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -16474,7 +15791,6 @@
           <t>(4,14)</t>
         </is>
       </c>
-      <c r="J464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -16504,7 +15820,6 @@
           <t>(4,15)</t>
         </is>
       </c>
-      <c r="J465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -16534,7 +15849,6 @@
           <t>(4,16)</t>
         </is>
       </c>
-      <c r="J466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -16564,7 +15878,6 @@
           <t>(4,17)</t>
         </is>
       </c>
-      <c r="J467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -16594,7 +15907,6 @@
           <t>(4,18)</t>
         </is>
       </c>
-      <c r="J468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -16624,7 +15936,6 @@
           <t>(4,19)</t>
         </is>
       </c>
-      <c r="J469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -16654,7 +15965,6 @@
           <t>(4,20)</t>
         </is>
       </c>
-      <c r="J470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -16684,7 +15994,6 @@
           <t>(4,21)</t>
         </is>
       </c>
-      <c r="J471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -16714,7 +16023,6 @@
           <t>(4,22)</t>
         </is>
       </c>
-      <c r="J472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -16744,7 +16052,6 @@
           <t>(4,23)</t>
         </is>
       </c>
-      <c r="J473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -16774,7 +16081,6 @@
           <t>(4,24)</t>
         </is>
       </c>
-      <c r="J474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -16804,7 +16110,6 @@
           <t>(4,25)</t>
         </is>
       </c>
-      <c r="J475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -16834,7 +16139,6 @@
           <t>(4,26)</t>
         </is>
       </c>
-      <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -16864,7 +16168,6 @@
           <t>(4,27)</t>
         </is>
       </c>
-      <c r="J477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -16894,7 +16197,6 @@
           <t>(5,6)</t>
         </is>
       </c>
-      <c r="J478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -16924,7 +16226,6 @@
           <t>(5,7)</t>
         </is>
       </c>
-      <c r="J479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -16954,7 +16255,6 @@
           <t>(5,8)</t>
         </is>
       </c>
-      <c r="J480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -16984,7 +16284,6 @@
           <t>(5,9)</t>
         </is>
       </c>
-      <c r="J481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -17014,7 +16313,6 @@
           <t>(5,10)</t>
         </is>
       </c>
-      <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -17044,7 +16342,6 @@
           <t>(5,11)</t>
         </is>
       </c>
-      <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -17074,7 +16371,6 @@
           <t>(5,12)</t>
         </is>
       </c>
-      <c r="J484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -17104,7 +16400,6 @@
           <t>(5,13)</t>
         </is>
       </c>
-      <c r="J485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -17134,7 +16429,6 @@
           <t>(5,14)</t>
         </is>
       </c>
-      <c r="J486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -17164,7 +16458,6 @@
           <t>(5,15)</t>
         </is>
       </c>
-      <c r="J487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -17194,7 +16487,6 @@
           <t>(5,16)</t>
         </is>
       </c>
-      <c r="J488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -17224,7 +16516,6 @@
           <t>(5,17)</t>
         </is>
       </c>
-      <c r="J489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -17254,7 +16545,6 @@
           <t>(5,18)</t>
         </is>
       </c>
-      <c r="J490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -17284,7 +16574,6 @@
           <t>(5,19)</t>
         </is>
       </c>
-      <c r="J491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -17314,7 +16603,6 @@
           <t>(5,20)</t>
         </is>
       </c>
-      <c r="J492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -17344,7 +16632,6 @@
           <t>(5,21)</t>
         </is>
       </c>
-      <c r="J493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -17374,7 +16661,6 @@
           <t>(5,22)</t>
         </is>
       </c>
-      <c r="J494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -17404,7 +16690,6 @@
           <t>(5,23)</t>
         </is>
       </c>
-      <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -17434,7 +16719,6 @@
           <t>(5,24)</t>
         </is>
       </c>
-      <c r="J496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -17464,7 +16748,6 @@
           <t>(5,25)</t>
         </is>
       </c>
-      <c r="J497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -17494,7 +16777,6 @@
           <t>(5,26)</t>
         </is>
       </c>
-      <c r="J498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -17524,7 +16806,6 @@
           <t>(5,27)</t>
         </is>
       </c>
-      <c r="J499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -17554,7 +16835,6 @@
           <t>(6,7)</t>
         </is>
       </c>
-      <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -17584,7 +16864,6 @@
           <t>(6,8)</t>
         </is>
       </c>
-      <c r="J501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -17614,7 +16893,6 @@
           <t>(6,9)</t>
         </is>
       </c>
-      <c r="J502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -17644,7 +16922,6 @@
           <t>(6,10)</t>
         </is>
       </c>
-      <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -17674,7 +16951,6 @@
           <t>(6,11)</t>
         </is>
       </c>
-      <c r="J504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -17704,7 +16980,6 @@
           <t>(6,12)</t>
         </is>
       </c>
-      <c r="J505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -17734,7 +17009,6 @@
           <t>(6,13)</t>
         </is>
       </c>
-      <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -17764,7 +17038,6 @@
           <t>(6,14)</t>
         </is>
       </c>
-      <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -17794,7 +17067,6 @@
           <t>(6,15)</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -17824,7 +17096,6 @@
           <t>(6,16)</t>
         </is>
       </c>
-      <c r="J509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -17854,7 +17125,6 @@
           <t>(6,17)</t>
         </is>
       </c>
-      <c r="J510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -17884,7 +17154,6 @@
           <t>(6,18)</t>
         </is>
       </c>
-      <c r="J511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -17914,7 +17183,6 @@
           <t>(6,19)</t>
         </is>
       </c>
-      <c r="J512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -17944,7 +17212,6 @@
           <t>(6,20)</t>
         </is>
       </c>
-      <c r="J513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -17974,7 +17241,6 @@
           <t>(6,21)</t>
         </is>
       </c>
-      <c r="J514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -18004,7 +17270,6 @@
           <t>(6,22)</t>
         </is>
       </c>
-      <c r="J515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -18034,7 +17299,6 @@
           <t>(6,23)</t>
         </is>
       </c>
-      <c r="J516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -18064,7 +17328,6 @@
           <t>(6,24)</t>
         </is>
       </c>
-      <c r="J517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -18094,7 +17357,6 @@
           <t>(6,25)</t>
         </is>
       </c>
-      <c r="J518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -18124,7 +17386,6 @@
           <t>(6,26)</t>
         </is>
       </c>
-      <c r="J519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -18154,7 +17415,6 @@
           <t>(6,27)</t>
         </is>
       </c>
-      <c r="J520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -18184,7 +17444,6 @@
           <t>(7,8)</t>
         </is>
       </c>
-      <c r="J521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -18214,7 +17473,6 @@
           <t>(7,9)</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -18244,7 +17502,6 @@
           <t>(7,10)</t>
         </is>
       </c>
-      <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -18274,7 +17531,6 @@
           <t>(7,11)</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -18304,7 +17560,6 @@
           <t>(7,12)</t>
         </is>
       </c>
-      <c r="J525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -18334,7 +17589,6 @@
           <t>(7,13)</t>
         </is>
       </c>
-      <c r="J526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -18364,7 +17618,6 @@
           <t>(7,14)</t>
         </is>
       </c>
-      <c r="J527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -18394,7 +17647,6 @@
           <t>(7,15)</t>
         </is>
       </c>
-      <c r="J528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -18424,7 +17676,6 @@
           <t>(7,16)</t>
         </is>
       </c>
-      <c r="J529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -18454,7 +17705,6 @@
           <t>(7,17)</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -18484,7 +17734,6 @@
           <t>(7,18)</t>
         </is>
       </c>
-      <c r="J531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -18514,7 +17763,6 @@
           <t>(7,19)</t>
         </is>
       </c>
-      <c r="J532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -18544,7 +17792,6 @@
           <t>(7,20)</t>
         </is>
       </c>
-      <c r="J533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -18574,7 +17821,6 @@
           <t>(7,21)</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -18604,7 +17850,6 @@
           <t>(7,22)</t>
         </is>
       </c>
-      <c r="J535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -18634,7 +17879,6 @@
           <t>(7,23)</t>
         </is>
       </c>
-      <c r="J536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -18664,7 +17908,6 @@
           <t>(7,24)</t>
         </is>
       </c>
-      <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -18694,7 +17937,6 @@
           <t>(7,25)</t>
         </is>
       </c>
-      <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -18724,7 +17966,6 @@
           <t>(7,26)</t>
         </is>
       </c>
-      <c r="J539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -18754,7 +17995,6 @@
           <t>(7,27)</t>
         </is>
       </c>
-      <c r="J540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -18784,7 +18024,6 @@
           <t>(8,9)</t>
         </is>
       </c>
-      <c r="J541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -18814,7 +18053,6 @@
           <t>(8,10)</t>
         </is>
       </c>
-      <c r="J542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -18844,7 +18082,6 @@
           <t>(8,11)</t>
         </is>
       </c>
-      <c r="J543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -18874,7 +18111,6 @@
           <t>(8,12)</t>
         </is>
       </c>
-      <c r="J544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -18904,7 +18140,6 @@
           <t>(8,13)</t>
         </is>
       </c>
-      <c r="J545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -18934,7 +18169,6 @@
           <t>(8,14)</t>
         </is>
       </c>
-      <c r="J546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -18964,7 +18198,6 @@
           <t>(8,15)</t>
         </is>
       </c>
-      <c r="J547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -18994,7 +18227,6 @@
           <t>(8,16)</t>
         </is>
       </c>
-      <c r="J548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -19024,7 +18256,6 @@
           <t>(8,17)</t>
         </is>
       </c>
-      <c r="J549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -19054,7 +18285,6 @@
           <t>(8,18)</t>
         </is>
       </c>
-      <c r="J550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -19084,7 +18314,6 @@
           <t>(8,19)</t>
         </is>
       </c>
-      <c r="J551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -19114,7 +18343,6 @@
           <t>(8,20)</t>
         </is>
       </c>
-      <c r="J552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -19144,7 +18372,6 @@
           <t>(8,21)</t>
         </is>
       </c>
-      <c r="J553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -19174,7 +18401,6 @@
           <t>(8,22)</t>
         </is>
       </c>
-      <c r="J554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -19204,7 +18430,6 @@
           <t>(8,23)</t>
         </is>
       </c>
-      <c r="J555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -19234,7 +18459,6 @@
           <t>(8,24)</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -19264,7 +18488,6 @@
           <t>(8,25)</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -19294,7 +18517,6 @@
           <t>(8,26)</t>
         </is>
       </c>
-      <c r="J558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -19324,7 +18546,6 @@
           <t>(8,27)</t>
         </is>
       </c>
-      <c r="J559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -19354,7 +18575,6 @@
           <t>(9,10)</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -19384,7 +18604,6 @@
           <t>(9,11)</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -19414,7 +18633,6 @@
           <t>(9,12)</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -19444,7 +18662,6 @@
           <t>(9,13)</t>
         </is>
       </c>
-      <c r="J563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -19474,7 +18691,6 @@
           <t>(9,14)</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -19504,7 +18720,6 @@
           <t>(9,15)</t>
         </is>
       </c>
-      <c r="J565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -19534,7 +18749,6 @@
           <t>(9,16)</t>
         </is>
       </c>
-      <c r="J566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -19564,7 +18778,6 @@
           <t>(9,17)</t>
         </is>
       </c>
-      <c r="J567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -19594,7 +18807,6 @@
           <t>(9,18)</t>
         </is>
       </c>
-      <c r="J568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -19624,7 +18836,6 @@
           <t>(9,19)</t>
         </is>
       </c>
-      <c r="J569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -19654,7 +18865,6 @@
           <t>(9,20)</t>
         </is>
       </c>
-      <c r="J570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -19684,7 +18894,6 @@
           <t>(9,21)</t>
         </is>
       </c>
-      <c r="J571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -19714,7 +18923,6 @@
           <t>(9,22)</t>
         </is>
       </c>
-      <c r="J572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -19744,7 +18952,6 @@
           <t>(9,23)</t>
         </is>
       </c>
-      <c r="J573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -19774,7 +18981,6 @@
           <t>(9,24)</t>
         </is>
       </c>
-      <c r="J574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -19804,7 +19010,6 @@
           <t>(9,25)</t>
         </is>
       </c>
-      <c r="J575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -19834,7 +19039,6 @@
           <t>(9,26)</t>
         </is>
       </c>
-      <c r="J576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -19864,7 +19068,6 @@
           <t>(9,27)</t>
         </is>
       </c>
-      <c r="J577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -19894,7 +19097,6 @@
           <t>(10,11)</t>
         </is>
       </c>
-      <c r="J578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -19924,7 +19126,6 @@
           <t>(10,12)</t>
         </is>
       </c>
-      <c r="J579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -19954,7 +19155,6 @@
           <t>(10,13)</t>
         </is>
       </c>
-      <c r="J580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -19984,7 +19184,6 @@
           <t>(10,14)</t>
         </is>
       </c>
-      <c r="J581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -20014,7 +19213,6 @@
           <t>(10,15)</t>
         </is>
       </c>
-      <c r="J582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -20044,7 +19242,6 @@
           <t>(10,16)</t>
         </is>
       </c>
-      <c r="J583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -20074,7 +19271,6 @@
           <t>(10,17)</t>
         </is>
       </c>
-      <c r="J584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -20104,7 +19300,6 @@
           <t>(10,18)</t>
         </is>
       </c>
-      <c r="J585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -20134,7 +19329,6 @@
           <t>(10,19)</t>
         </is>
       </c>
-      <c r="J586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -20164,7 +19358,6 @@
           <t>(10,20)</t>
         </is>
       </c>
-      <c r="J587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -20194,7 +19387,6 @@
           <t>(10,21)</t>
         </is>
       </c>
-      <c r="J588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -20224,7 +19416,6 @@
           <t>(10,22)</t>
         </is>
       </c>
-      <c r="J589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -20254,7 +19445,6 @@
           <t>(10,23)</t>
         </is>
       </c>
-      <c r="J590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -20284,7 +19474,6 @@
           <t>(10,24)</t>
         </is>
       </c>
-      <c r="J591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -20314,7 +19503,6 @@
           <t>(10,25)</t>
         </is>
       </c>
-      <c r="J592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -20344,7 +19532,6 @@
           <t>(10,26)</t>
         </is>
       </c>
-      <c r="J593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -20374,7 +19561,6 @@
           <t>(10,27)</t>
         </is>
       </c>
-      <c r="J594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -20404,7 +19590,6 @@
           <t>(11,12)</t>
         </is>
       </c>
-      <c r="J595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -20434,7 +19619,6 @@
           <t>(11,13)</t>
         </is>
       </c>
-      <c r="J596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -20464,7 +19648,6 @@
           <t>(11,14)</t>
         </is>
       </c>
-      <c r="J597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -20494,7 +19677,6 @@
           <t>(11,15)</t>
         </is>
       </c>
-      <c r="J598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -20524,7 +19706,6 @@
           <t>(11,16)</t>
         </is>
       </c>
-      <c r="J599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -20554,7 +19735,6 @@
           <t>(11,17)</t>
         </is>
       </c>
-      <c r="J600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -20584,7 +19764,6 @@
           <t>(11,18)</t>
         </is>
       </c>
-      <c r="J601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -20614,7 +19793,6 @@
           <t>(11,19)</t>
         </is>
       </c>
-      <c r="J602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -20644,7 +19822,6 @@
           <t>(11,20)</t>
         </is>
       </c>
-      <c r="J603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -20674,7 +19851,6 @@
           <t>(11,21)</t>
         </is>
       </c>
-      <c r="J604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -20704,7 +19880,6 @@
           <t>(11,22)</t>
         </is>
       </c>
-      <c r="J605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -20734,7 +19909,6 @@
           <t>(11,23)</t>
         </is>
       </c>
-      <c r="J606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -20764,7 +19938,6 @@
           <t>(11,24)</t>
         </is>
       </c>
-      <c r="J607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -20794,7 +19967,6 @@
           <t>(11,25)</t>
         </is>
       </c>
-      <c r="J608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -20824,7 +19996,6 @@
           <t>(11,26)</t>
         </is>
       </c>
-      <c r="J609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -20854,7 +20025,6 @@
           <t>(11,27)</t>
         </is>
       </c>
-      <c r="J610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -20884,7 +20054,6 @@
           <t>(12,13)</t>
         </is>
       </c>
-      <c r="J611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -20914,7 +20083,6 @@
           <t>(12,14)</t>
         </is>
       </c>
-      <c r="J612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -20944,7 +20112,6 @@
           <t>(12,15)</t>
         </is>
       </c>
-      <c r="J613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -20974,7 +20141,6 @@
           <t>(12,16)</t>
         </is>
       </c>
-      <c r="J614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -21004,7 +20170,6 @@
           <t>(12,17)</t>
         </is>
       </c>
-      <c r="J615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -21034,7 +20199,6 @@
           <t>(12,18)</t>
         </is>
       </c>
-      <c r="J616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -21064,7 +20228,6 @@
           <t>(12,19)</t>
         </is>
       </c>
-      <c r="J617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -21094,7 +20257,6 @@
           <t>(12,20)</t>
         </is>
       </c>
-      <c r="J618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -21124,7 +20286,6 @@
           <t>(12,21)</t>
         </is>
       </c>
-      <c r="J619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -21154,7 +20315,6 @@
           <t>(12,22)</t>
         </is>
       </c>
-      <c r="J620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -21184,7 +20344,6 @@
           <t>(12,23)</t>
         </is>
       </c>
-      <c r="J621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -21214,7 +20373,6 @@
           <t>(12,24)</t>
         </is>
       </c>
-      <c r="J622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -21244,7 +20402,6 @@
           <t>(12,25)</t>
         </is>
       </c>
-      <c r="J623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -21274,7 +20431,6 @@
           <t>(12,26)</t>
         </is>
       </c>
-      <c r="J624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -21304,7 +20460,6 @@
           <t>(12,27)</t>
         </is>
       </c>
-      <c r="J625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -21334,7 +20489,6 @@
           <t>(13,14)</t>
         </is>
       </c>
-      <c r="J626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -21364,7 +20518,6 @@
           <t>(13,15)</t>
         </is>
       </c>
-      <c r="J627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -21394,7 +20547,6 @@
           <t>(13,16)</t>
         </is>
       </c>
-      <c r="J628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -21424,7 +20576,6 @@
           <t>(13,17)</t>
         </is>
       </c>
-      <c r="J629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -21454,7 +20605,6 @@
           <t>(13,18)</t>
         </is>
       </c>
-      <c r="J630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -21484,7 +20634,6 @@
           <t>(13,19)</t>
         </is>
       </c>
-      <c r="J631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -21514,7 +20663,6 @@
           <t>(13,20)</t>
         </is>
       </c>
-      <c r="J632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -21544,7 +20692,6 @@
           <t>(13,21)</t>
         </is>
       </c>
-      <c r="J633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -21574,7 +20721,6 @@
           <t>(13,22)</t>
         </is>
       </c>
-      <c r="J634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -21604,7 +20750,6 @@
           <t>(13,23)</t>
         </is>
       </c>
-      <c r="J635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -21634,7 +20779,6 @@
           <t>(13,24)</t>
         </is>
       </c>
-      <c r="J636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -21664,7 +20808,6 @@
           <t>(13,25)</t>
         </is>
       </c>
-      <c r="J637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -21694,7 +20837,6 @@
           <t>(13,26)</t>
         </is>
       </c>
-      <c r="J638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -21724,7 +20866,6 @@
           <t>(13,27)</t>
         </is>
       </c>
-      <c r="J639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -21754,7 +20895,6 @@
           <t>(14,15)</t>
         </is>
       </c>
-      <c r="J640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -21784,7 +20924,6 @@
           <t>(14,16)</t>
         </is>
       </c>
-      <c r="J641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -21814,7 +20953,6 @@
           <t>(14,17)</t>
         </is>
       </c>
-      <c r="J642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -21844,7 +20982,6 @@
           <t>(14,18)</t>
         </is>
       </c>
-      <c r="J643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -21874,7 +21011,6 @@
           <t>(14,19)</t>
         </is>
       </c>
-      <c r="J644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -21904,7 +21040,6 @@
           <t>(14,20)</t>
         </is>
       </c>
-      <c r="J645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -21934,7 +21069,6 @@
           <t>(14,21)</t>
         </is>
       </c>
-      <c r="J646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -21964,7 +21098,6 @@
           <t>(14,22)</t>
         </is>
       </c>
-      <c r="J647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -21994,7 +21127,6 @@
           <t>(14,23)</t>
         </is>
       </c>
-      <c r="J648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -22024,7 +21156,6 @@
           <t>(14,24)</t>
         </is>
       </c>
-      <c r="J649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -22054,7 +21185,6 @@
           <t>(14,25)</t>
         </is>
       </c>
-      <c r="J650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -22084,7 +21214,6 @@
           <t>(14,26)</t>
         </is>
       </c>
-      <c r="J651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -22114,7 +21243,6 @@
           <t>(14,27)</t>
         </is>
       </c>
-      <c r="J652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -22144,7 +21272,6 @@
           <t>(15,16)</t>
         </is>
       </c>
-      <c r="J653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -22174,7 +21301,6 @@
           <t>(15,17)</t>
         </is>
       </c>
-      <c r="J654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -22204,7 +21330,6 @@
           <t>(15,18)</t>
         </is>
       </c>
-      <c r="J655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -22234,7 +21359,6 @@
           <t>(15,19)</t>
         </is>
       </c>
-      <c r="J656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -22264,7 +21388,6 @@
           <t>(15,20)</t>
         </is>
       </c>
-      <c r="J657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -22294,7 +21417,6 @@
           <t>(15,21)</t>
         </is>
       </c>
-      <c r="J658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -22324,7 +21446,6 @@
           <t>(15,22)</t>
         </is>
       </c>
-      <c r="J659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -22354,7 +21475,6 @@
           <t>(15,23)</t>
         </is>
       </c>
-      <c r="J660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -22384,7 +21504,6 @@
           <t>(15,24)</t>
         </is>
       </c>
-      <c r="J661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -22414,7 +21533,6 @@
           <t>(15,25)</t>
         </is>
       </c>
-      <c r="J662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -22444,7 +21562,6 @@
           <t>(15,26)</t>
         </is>
       </c>
-      <c r="J663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -22474,7 +21591,6 @@
           <t>(15,27)</t>
         </is>
       </c>
-      <c r="J664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -22504,7 +21620,6 @@
           <t>(16,17)</t>
         </is>
       </c>
-      <c r="J665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -22534,7 +21649,6 @@
           <t>(16,18)</t>
         </is>
       </c>
-      <c r="J666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -22564,7 +21678,6 @@
           <t>(16,19)</t>
         </is>
       </c>
-      <c r="J667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -22594,7 +21707,6 @@
           <t>(16,20)</t>
         </is>
       </c>
-      <c r="J668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -22624,7 +21736,6 @@
           <t>(16,21)</t>
         </is>
       </c>
-      <c r="J669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -22654,7 +21765,6 @@
           <t>(16,22)</t>
         </is>
       </c>
-      <c r="J670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -22684,7 +21794,6 @@
           <t>(16,23)</t>
         </is>
       </c>
-      <c r="J671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -22714,7 +21823,6 @@
           <t>(16,24)</t>
         </is>
       </c>
-      <c r="J672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -22744,7 +21852,6 @@
           <t>(16,25)</t>
         </is>
       </c>
-      <c r="J673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -22774,7 +21881,6 @@
           <t>(16,26)</t>
         </is>
       </c>
-      <c r="J674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -22804,7 +21910,6 @@
           <t>(16,27)</t>
         </is>
       </c>
-      <c r="J675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -22834,7 +21939,6 @@
           <t>(17,18)</t>
         </is>
       </c>
-      <c r="J676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -22864,7 +21968,6 @@
           <t>(17,19)</t>
         </is>
       </c>
-      <c r="J677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -22894,7 +21997,6 @@
           <t>(17,20)</t>
         </is>
       </c>
-      <c r="J678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -22924,7 +22026,6 @@
           <t>(17,21)</t>
         </is>
       </c>
-      <c r="J679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -22954,7 +22055,6 @@
           <t>(17,22)</t>
         </is>
       </c>
-      <c r="J680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -22984,7 +22084,6 @@
           <t>(17,23)</t>
         </is>
       </c>
-      <c r="J681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -23014,7 +22113,6 @@
           <t>(17,24)</t>
         </is>
       </c>
-      <c r="J682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -23044,7 +22142,6 @@
           <t>(17,25)</t>
         </is>
       </c>
-      <c r="J683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -23074,7 +22171,6 @@
           <t>(17,26)</t>
         </is>
       </c>
-      <c r="J684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -23104,7 +22200,6 @@
           <t>(17,27)</t>
         </is>
       </c>
-      <c r="J685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -23134,7 +22229,6 @@
           <t>(18,19)</t>
         </is>
       </c>
-      <c r="J686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -23164,7 +22258,6 @@
           <t>(18,20)</t>
         </is>
       </c>
-      <c r="J687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -23194,7 +22287,6 @@
           <t>(18,21)</t>
         </is>
       </c>
-      <c r="J688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -23224,7 +22316,6 @@
           <t>(18,22)</t>
         </is>
       </c>
-      <c r="J689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -23254,7 +22345,6 @@
           <t>(18,23)</t>
         </is>
       </c>
-      <c r="J690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -23284,7 +22374,6 @@
           <t>(18,24)</t>
         </is>
       </c>
-      <c r="J691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -23314,7 +22403,6 @@
           <t>(18,25)</t>
         </is>
       </c>
-      <c r="J692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -23344,7 +22432,6 @@
           <t>(18,26)</t>
         </is>
       </c>
-      <c r="J693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -23374,7 +22461,6 @@
           <t>(18,27)</t>
         </is>
       </c>
-      <c r="J694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -23404,7 +22490,6 @@
           <t>(19,20)</t>
         </is>
       </c>
-      <c r="J695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -23434,7 +22519,6 @@
           <t>(19,21)</t>
         </is>
       </c>
-      <c r="J696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -23464,7 +22548,6 @@
           <t>(19,22)</t>
         </is>
       </c>
-      <c r="J697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -23494,7 +22577,6 @@
           <t>(19,23)</t>
         </is>
       </c>
-      <c r="J698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -23524,7 +22606,6 @@
           <t>(19,24)</t>
         </is>
       </c>
-      <c r="J699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -23554,7 +22635,6 @@
           <t>(19,25)</t>
         </is>
       </c>
-      <c r="J700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -23584,7 +22664,6 @@
           <t>(19,26)</t>
         </is>
       </c>
-      <c r="J701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -23614,7 +22693,6 @@
           <t>(19,27)</t>
         </is>
       </c>
-      <c r="J702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -23644,7 +22722,6 @@
           <t>(20,21)</t>
         </is>
       </c>
-      <c r="J703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -23674,7 +22751,6 @@
           <t>(20,22)</t>
         </is>
       </c>
-      <c r="J704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -23704,7 +22780,6 @@
           <t>(20,23)</t>
         </is>
       </c>
-      <c r="J705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -23734,7 +22809,6 @@
           <t>(20,24)</t>
         </is>
       </c>
-      <c r="J706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -23764,7 +22838,6 @@
           <t>(20,25)</t>
         </is>
       </c>
-      <c r="J707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -23794,7 +22867,6 @@
           <t>(20,26)</t>
         </is>
       </c>
-      <c r="J708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -23824,7 +22896,6 @@
           <t>(20,27)</t>
         </is>
       </c>
-      <c r="J709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -23854,7 +22925,6 @@
           <t>(21,22)</t>
         </is>
       </c>
-      <c r="J710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -23884,7 +22954,6 @@
           <t>(21,23)</t>
         </is>
       </c>
-      <c r="J711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -23914,7 +22983,6 @@
           <t>(21,24)</t>
         </is>
       </c>
-      <c r="J712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -23944,7 +23012,6 @@
           <t>(21,25)</t>
         </is>
       </c>
-      <c r="J713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -23974,7 +23041,6 @@
           <t>(21,26)</t>
         </is>
       </c>
-      <c r="J714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -24004,7 +23070,6 @@
           <t>(21,27)</t>
         </is>
       </c>
-      <c r="J715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -24034,7 +23099,6 @@
           <t>(22,23)</t>
         </is>
       </c>
-      <c r="J716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -24064,7 +23128,6 @@
           <t>(22,24)</t>
         </is>
       </c>
-      <c r="J717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -24094,7 +23157,6 @@
           <t>(22,25)</t>
         </is>
       </c>
-      <c r="J718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -24124,7 +23186,6 @@
           <t>(22,26)</t>
         </is>
       </c>
-      <c r="J719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -24154,7 +23215,6 @@
           <t>(22,27)</t>
         </is>
       </c>
-      <c r="J720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -24184,7 +23244,6 @@
           <t>(23,24)</t>
         </is>
       </c>
-      <c r="J721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -24214,7 +23273,6 @@
           <t>(23,25)</t>
         </is>
       </c>
-      <c r="J722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -24244,7 +23302,6 @@
           <t>(23,26)</t>
         </is>
       </c>
-      <c r="J723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -24274,7 +23331,6 @@
           <t>(23,27)</t>
         </is>
       </c>
-      <c r="J724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -24304,7 +23360,6 @@
           <t>(24,25)</t>
         </is>
       </c>
-      <c r="J725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -24334,7 +23389,6 @@
           <t>(24,26)</t>
         </is>
       </c>
-      <c r="J726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -24364,7 +23418,6 @@
           <t>(24,27)</t>
         </is>
       </c>
-      <c r="J727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -24394,7 +23447,6 @@
           <t>(25,26)</t>
         </is>
       </c>
-      <c r="J728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -24424,7 +23476,6 @@
           <t>(25,27)</t>
         </is>
       </c>
-      <c r="J729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -24454,7 +23505,6 @@
           <t>(26,27)</t>
         </is>
       </c>
-      <c r="J730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -24480,7 +23530,6 @@
         </is>
       </c>
       <c r="I731" t="inlineStr"/>
-      <c r="J731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -24506,7 +23555,6 @@
         </is>
       </c>
       <c r="I732" t="inlineStr"/>
-      <c r="J732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -24532,7 +23580,6 @@
         </is>
       </c>
       <c r="I733" t="inlineStr"/>
-      <c r="J733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -24558,7 +23605,6 @@
         </is>
       </c>
       <c r="I734" t="inlineStr"/>
-      <c r="J734" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
